--- a/Checklist_Riesgos_Centro_Distribucion.xlsx
+++ b/Checklist_Riesgos_Centro_Distribucion.xlsx
@@ -3320,15 +3320,15 @@
       </c>
       <c r="K5" s="17">
         <f>IF(OR($I5="",$J5=""),"",$I5*$J5)</f>
-        <v/>
-      </c>
-      <c r="L5" s="17">
+        <v>10</v>
+      </c>
+      <c r="L5" s="17" t="str">
         <f>IF($K5="","",IF($K5&gt;=20,"Extremo",IF($K5&gt;=12,"Alto",IF($K5&gt;=6,"Medio",IF($K5&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M5" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M5" s="8" t="str">
         <f>IFERROR(VLOOKUP($L5,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N5" s="8" t="inlineStr">
         <is>
@@ -3399,15 +3399,15 @@
       </c>
       <c r="K6" s="17">
         <f>IF(OR($I6="",$J6=""),"",$I6*$J6)</f>
-        <v/>
-      </c>
-      <c r="L6" s="17">
+        <v>12</v>
+      </c>
+      <c r="L6" s="17" t="str">
         <f>IF($K6="","",IF($K6&gt;=20,"Extremo",IF($K6&gt;=12,"Alto",IF($K6&gt;=6,"Medio",IF($K6&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M6" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M6" s="8" t="str">
         <f>IFERROR(VLOOKUP($L6,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
@@ -3478,15 +3478,15 @@
       </c>
       <c r="K7" s="17">
         <f>IF(OR($I7="",$J7=""),"",$I7*$J7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="17">
+        <v>12</v>
+      </c>
+      <c r="L7" s="17" t="str">
         <f>IF($K7="","",IF($K7&gt;=20,"Extremo",IF($K7&gt;=12,"Alto",IF($K7&gt;=6,"Medio",IF($K7&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M7" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M7" s="8" t="str">
         <f>IFERROR(VLOOKUP($L7,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
@@ -3557,15 +3557,15 @@
       </c>
       <c r="K8" s="17">
         <f>IF(OR($I8="",$J8=""),"",$I8*$J8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="17">
+        <v>15</v>
+      </c>
+      <c r="L8" s="17" t="str">
         <f>IF($K8="","",IF($K8&gt;=20,"Extremo",IF($K8&gt;=12,"Alto",IF($K8&gt;=6,"Medio",IF($K8&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M8" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M8" s="8" t="str">
         <f>IFERROR(VLOOKUP($L8,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
@@ -3636,15 +3636,15 @@
       </c>
       <c r="K9" s="17">
         <f>IF(OR($I9="",$J9=""),"",$I9*$J9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="17">
+        <v>9</v>
+      </c>
+      <c r="L9" s="17" t="str">
         <f>IF($K9="","",IF($K9&gt;=20,"Extremo",IF($K9&gt;=12,"Alto",IF($K9&gt;=6,"Medio",IF($K9&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M9" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M9" s="8" t="str">
         <f>IFERROR(VLOOKUP($L9,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
@@ -3715,15 +3715,15 @@
       </c>
       <c r="K10" s="17">
         <f>IF(OR($I10="",$J10=""),"",$I10*$J10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="17">
+        <v>20</v>
+      </c>
+      <c r="L10" s="17" t="str">
         <f>IF($K10="","",IF($K10&gt;=20,"Extremo",IF($K10&gt;=12,"Alto",IF($K10&gt;=6,"Medio",IF($K10&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M10" s="8">
+        <v>Extremo</v>
+      </c>
+      <c r="M10" s="8" t="str">
         <f>IFERROR(VLOOKUP($L10,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Diaria o por turno (verificación operativa) + inspección formal semanal documentada</v>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
@@ -3794,15 +3794,15 @@
       </c>
       <c r="K11" s="17">
         <f>IF(OR($I11="",$J11=""),"",$I11*$J11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="17">
+        <v>20</v>
+      </c>
+      <c r="L11" s="17" t="str">
         <f>IF($K11="","",IF($K11&gt;=20,"Extremo",IF($K11&gt;=12,"Alto",IF($K11&gt;=6,"Medio",IF($K11&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M11" s="8">
+        <v>Extremo</v>
+      </c>
+      <c r="M11" s="8" t="str">
         <f>IFERROR(VLOOKUP($L11,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Diaria o por turno (verificación operativa) + inspección formal semanal documentada</v>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
@@ -3873,15 +3873,15 @@
       </c>
       <c r="K12" s="17">
         <f>IF(OR($I12="",$J12=""),"",$I12*$J12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="17">
+        <v>20</v>
+      </c>
+      <c r="L12" s="17" t="str">
         <f>IF($K12="","",IF($K12&gt;=20,"Extremo",IF($K12&gt;=12,"Alto",IF($K12&gt;=6,"Medio",IF($K12&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M12" s="8">
+        <v>Extremo</v>
+      </c>
+      <c r="M12" s="8" t="str">
         <f>IFERROR(VLOOKUP($L12,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Diaria o por turno (verificación operativa) + inspección formal semanal documentada</v>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
@@ -3952,15 +3952,15 @@
       </c>
       <c r="K13" s="17">
         <f>IF(OR($I13="",$J13=""),"",$I13*$J13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="17">
+        <v>15</v>
+      </c>
+      <c r="L13" s="17" t="str">
         <f>IF($K13="","",IF($K13&gt;=20,"Extremo",IF($K13&gt;=12,"Alto",IF($K13&gt;=6,"Medio",IF($K13&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M13" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M13" s="8" t="str">
         <f>IFERROR(VLOOKUP($L13,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
@@ -4031,15 +4031,15 @@
       </c>
       <c r="K14" s="17">
         <f>IF(OR($I14="",$J14=""),"",$I14*$J14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="17">
+        <v>15</v>
+      </c>
+      <c r="L14" s="17" t="str">
         <f>IF($K14="","",IF($K14&gt;=20,"Extremo",IF($K14&gt;=12,"Alto",IF($K14&gt;=6,"Medio",IF($K14&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M14" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M14" s="8" t="str">
         <f>IFERROR(VLOOKUP($L14,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
@@ -4110,15 +4110,15 @@
       </c>
       <c r="K15" s="17">
         <f>IF(OR($I15="",$J15=""),"",$I15*$J15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="17">
+        <v>12</v>
+      </c>
+      <c r="L15" s="17" t="str">
         <f>IF($K15="","",IF($K15&gt;=20,"Extremo",IF($K15&gt;=12,"Alto",IF($K15&gt;=6,"Medio",IF($K15&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M15" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M15" s="8" t="str">
         <f>IFERROR(VLOOKUP($L15,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
@@ -4189,15 +4189,15 @@
       </c>
       <c r="K16" s="17">
         <f>IF(OR($I16="",$J16=""),"",$I16*$J16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="17">
+        <v>15</v>
+      </c>
+      <c r="L16" s="17" t="str">
         <f>IF($K16="","",IF($K16&gt;=20,"Extremo",IF($K16&gt;=12,"Alto",IF($K16&gt;=6,"Medio",IF($K16&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M16" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M16" s="8" t="str">
         <f>IFERROR(VLOOKUP($L16,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
@@ -4268,15 +4268,15 @@
       </c>
       <c r="K17" s="17">
         <f>IF(OR($I17="",$J17=""),"",$I17*$J17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="17">
+        <v>16</v>
+      </c>
+      <c r="L17" s="17" t="str">
         <f>IF($K17="","",IF($K17&gt;=20,"Extremo",IF($K17&gt;=12,"Alto",IF($K17&gt;=6,"Medio",IF($K17&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M17" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M17" s="8" t="str">
         <f>IFERROR(VLOOKUP($L17,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
@@ -4347,15 +4347,15 @@
       </c>
       <c r="K18" s="17">
         <f>IF(OR($I18="",$J18=""),"",$I18*$J18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="17">
+        <v>15</v>
+      </c>
+      <c r="L18" s="17" t="str">
         <f>IF($K18="","",IF($K18&gt;=20,"Extremo",IF($K18&gt;=12,"Alto",IF($K18&gt;=6,"Medio",IF($K18&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M18" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M18" s="8" t="str">
         <f>IFERROR(VLOOKUP($L18,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
@@ -4426,15 +4426,15 @@
       </c>
       <c r="K19" s="17">
         <f>IF(OR($I19="",$J19=""),"",$I19*$J19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="17">
+        <v>16</v>
+      </c>
+      <c r="L19" s="17" t="str">
         <f>IF($K19="","",IF($K19&gt;=20,"Extremo",IF($K19&gt;=12,"Alto",IF($K19&gt;=6,"Medio",IF($K19&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M19" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M19" s="8" t="str">
         <f>IFERROR(VLOOKUP($L19,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
@@ -4505,15 +4505,15 @@
       </c>
       <c r="K20" s="17">
         <f>IF(OR($I20="",$J20=""),"",$I20*$J20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="17">
+        <v>16</v>
+      </c>
+      <c r="L20" s="17" t="str">
         <f>IF($K20="","",IF($K20&gt;=20,"Extremo",IF($K20&gt;=12,"Alto",IF($K20&gt;=6,"Medio",IF($K20&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M20" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M20" s="8" t="str">
         <f>IFERROR(VLOOKUP($L20,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
@@ -4584,15 +4584,15 @@
       </c>
       <c r="K21" s="17">
         <f>IF(OR($I21="",$J21=""),"",$I21*$J21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="17">
+        <v>15</v>
+      </c>
+      <c r="L21" s="17" t="str">
         <f>IF($K21="","",IF($K21&gt;=20,"Extremo",IF($K21&gt;=12,"Alto",IF($K21&gt;=6,"Medio",IF($K21&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M21" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M21" s="8" t="str">
         <f>IFERROR(VLOOKUP($L21,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
@@ -4663,15 +4663,15 @@
       </c>
       <c r="K22" s="17">
         <f>IF(OR($I22="",$J22=""),"",$I22*$J22)</f>
-        <v/>
-      </c>
-      <c r="L22" s="17">
+        <v>10</v>
+      </c>
+      <c r="L22" s="17" t="str">
         <f>IF($K22="","",IF($K22&gt;=20,"Extremo",IF($K22&gt;=12,"Alto",IF($K22&gt;=6,"Medio",IF($K22&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M22" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M22" s="8" t="str">
         <f>IFERROR(VLOOKUP($L22,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
@@ -4742,15 +4742,15 @@
       </c>
       <c r="K23" s="17">
         <f>IF(OR($I23="",$J23=""),"",$I23*$J23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="17">
+        <v>16</v>
+      </c>
+      <c r="L23" s="17" t="str">
         <f>IF($K23="","",IF($K23&gt;=20,"Extremo",IF($K23&gt;=12,"Alto",IF($K23&gt;=6,"Medio",IF($K23&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M23" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M23" s="8" t="str">
         <f>IFERROR(VLOOKUP($L23,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
@@ -4821,15 +4821,15 @@
       </c>
       <c r="K24" s="17">
         <f>IF(OR($I24="",$J24=""),"",$I24*$J24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="17">
+        <v>15</v>
+      </c>
+      <c r="L24" s="17" t="str">
         <f>IF($K24="","",IF($K24&gt;=20,"Extremo",IF($K24&gt;=12,"Alto",IF($K24&gt;=6,"Medio",IF($K24&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M24" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M24" s="8" t="str">
         <f>IFERROR(VLOOKUP($L24,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
@@ -4900,15 +4900,15 @@
       </c>
       <c r="K25" s="17">
         <f>IF(OR($I25="",$J25=""),"",$I25*$J25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="17">
+        <v>20</v>
+      </c>
+      <c r="L25" s="17" t="str">
         <f>IF($K25="","",IF($K25&gt;=20,"Extremo",IF($K25&gt;=12,"Alto",IF($K25&gt;=6,"Medio",IF($K25&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M25" s="8">
+        <v>Extremo</v>
+      </c>
+      <c r="M25" s="8" t="str">
         <f>IFERROR(VLOOKUP($L25,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Diaria o por turno (verificación operativa) + inspección formal semanal documentada</v>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
@@ -4979,15 +4979,15 @@
       </c>
       <c r="K26" s="17">
         <f>IF(OR($I26="",$J26=""),"",$I26*$J26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="17">
+        <v>10</v>
+      </c>
+      <c r="L26" s="17" t="str">
         <f>IF($K26="","",IF($K26&gt;=20,"Extremo",IF($K26&gt;=12,"Alto",IF($K26&gt;=6,"Medio",IF($K26&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M26" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M26" s="8" t="str">
         <f>IFERROR(VLOOKUP($L26,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
@@ -5058,15 +5058,15 @@
       </c>
       <c r="K27" s="17">
         <f>IF(OR($I27="",$J27=""),"",$I27*$J27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="17">
+        <v>12</v>
+      </c>
+      <c r="L27" s="17" t="str">
         <f>IF($K27="","",IF($K27&gt;=20,"Extremo",IF($K27&gt;=12,"Alto",IF($K27&gt;=6,"Medio",IF($K27&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M27" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M27" s="8" t="str">
         <f>IFERROR(VLOOKUP($L27,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
@@ -5137,15 +5137,15 @@
       </c>
       <c r="K28" s="17">
         <f>IF(OR($I28="",$J28=""),"",$I28*$J28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="17">
+        <v>12</v>
+      </c>
+      <c r="L28" s="17" t="str">
         <f>IF($K28="","",IF($K28&gt;=20,"Extremo",IF($K28&gt;=12,"Alto",IF($K28&gt;=6,"Medio",IF($K28&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M28" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M28" s="8" t="str">
         <f>IFERROR(VLOOKUP($L28,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
@@ -5216,15 +5216,15 @@
       </c>
       <c r="K29" s="17">
         <f>IF(OR($I29="",$J29=""),"",$I29*$J29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="17">
+        <v>15</v>
+      </c>
+      <c r="L29" s="17" t="str">
         <f>IF($K29="","",IF($K29&gt;=20,"Extremo",IF($K29&gt;=12,"Alto",IF($K29&gt;=6,"Medio",IF($K29&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M29" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M29" s="8" t="str">
         <f>IFERROR(VLOOKUP($L29,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
@@ -5295,15 +5295,15 @@
       </c>
       <c r="K30" s="17">
         <f>IF(OR($I30="",$J30=""),"",$I30*$J30)</f>
-        <v/>
-      </c>
-      <c r="L30" s="17">
+        <v>15</v>
+      </c>
+      <c r="L30" s="17" t="str">
         <f>IF($K30="","",IF($K30&gt;=20,"Extremo",IF($K30&gt;=12,"Alto",IF($K30&gt;=6,"Medio",IF($K30&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M30" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M30" s="8" t="str">
         <f>IFERROR(VLOOKUP($L30,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
@@ -5374,15 +5374,15 @@
       </c>
       <c r="K31" s="17">
         <f>IF(OR($I31="",$J31=""),"",$I31*$J31)</f>
-        <v/>
-      </c>
-      <c r="L31" s="17">
+        <v>12</v>
+      </c>
+      <c r="L31" s="17" t="str">
         <f>IF($K31="","",IF($K31&gt;=20,"Extremo",IF($K31&gt;=12,"Alto",IF($K31&gt;=6,"Medio",IF($K31&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M31" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M31" s="8" t="str">
         <f>IFERROR(VLOOKUP($L31,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
@@ -5453,15 +5453,15 @@
       </c>
       <c r="K32" s="17">
         <f>IF(OR($I32="",$J32=""),"",$I32*$J32)</f>
-        <v/>
-      </c>
-      <c r="L32" s="17">
+        <v>9</v>
+      </c>
+      <c r="L32" s="17" t="str">
         <f>IF($K32="","",IF($K32&gt;=20,"Extremo",IF($K32&gt;=12,"Alto",IF($K32&gt;=6,"Medio",IF($K32&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M32" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M32" s="8" t="str">
         <f>IFERROR(VLOOKUP($L32,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
@@ -5532,15 +5532,15 @@
       </c>
       <c r="K33" s="17">
         <f>IF(OR($I33="",$J33=""),"",$I33*$J33)</f>
-        <v/>
-      </c>
-      <c r="L33" s="17">
+        <v>16</v>
+      </c>
+      <c r="L33" s="17" t="str">
         <f>IF($K33="","",IF($K33&gt;=20,"Extremo",IF($K33&gt;=12,"Alto",IF($K33&gt;=6,"Medio",IF($K33&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M33" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M33" s="8" t="str">
         <f>IFERROR(VLOOKUP($L33,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
@@ -5611,15 +5611,15 @@
       </c>
       <c r="K34" s="17">
         <f>IF(OR($I34="",$J34=""),"",$I34*$J34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="17">
+        <v>12</v>
+      </c>
+      <c r="L34" s="17" t="str">
         <f>IF($K34="","",IF($K34&gt;=20,"Extremo",IF($K34&gt;=12,"Alto",IF($K34&gt;=6,"Medio",IF($K34&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M34" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M34" s="8" t="str">
         <f>IFERROR(VLOOKUP($L34,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
@@ -5690,15 +5690,15 @@
       </c>
       <c r="K35" s="17">
         <f>IF(OR($I35="",$J35=""),"",$I35*$J35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="17">
+        <v>9</v>
+      </c>
+      <c r="L35" s="17" t="str">
         <f>IF($K35="","",IF($K35&gt;=20,"Extremo",IF($K35&gt;=12,"Alto",IF($K35&gt;=6,"Medio",IF($K35&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M35" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M35" s="8" t="str">
         <f>IFERROR(VLOOKUP($L35,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
@@ -5769,15 +5769,15 @@
       </c>
       <c r="K36" s="17">
         <f>IF(OR($I36="",$J36=""),"",$I36*$J36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="17">
+        <v>15</v>
+      </c>
+      <c r="L36" s="17" t="str">
         <f>IF($K36="","",IF($K36&gt;=20,"Extremo",IF($K36&gt;=12,"Alto",IF($K36&gt;=6,"Medio",IF($K36&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M36" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M36" s="8" t="str">
         <f>IFERROR(VLOOKUP($L36,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
@@ -5848,15 +5848,15 @@
       </c>
       <c r="K37" s="17">
         <f>IF(OR($I37="",$J37=""),"",$I37*$J37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="17">
+        <v>8</v>
+      </c>
+      <c r="L37" s="17" t="str">
         <f>IF($K37="","",IF($K37&gt;=20,"Extremo",IF($K37&gt;=12,"Alto",IF($K37&gt;=6,"Medio",IF($K37&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M37" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M37" s="8" t="str">
         <f>IFERROR(VLOOKUP($L37,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
@@ -5927,15 +5927,15 @@
       </c>
       <c r="K38" s="17">
         <f>IF(OR($I38="",$J38=""),"",$I38*$J38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="17">
+        <v>9</v>
+      </c>
+      <c r="L38" s="17" t="str">
         <f>IF($K38="","",IF($K38&gt;=20,"Extremo",IF($K38&gt;=12,"Alto",IF($K38&gt;=6,"Medio",IF($K38&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M38" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M38" s="8" t="str">
         <f>IFERROR(VLOOKUP($L38,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
@@ -6006,15 +6006,15 @@
       </c>
       <c r="K39" s="17">
         <f>IF(OR($I39="",$J39=""),"",$I39*$J39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="17">
+        <v>20</v>
+      </c>
+      <c r="L39" s="17" t="str">
         <f>IF($K39="","",IF($K39&gt;=20,"Extremo",IF($K39&gt;=12,"Alto",IF($K39&gt;=6,"Medio",IF($K39&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M39" s="8">
+        <v>Extremo</v>
+      </c>
+      <c r="M39" s="8" t="str">
         <f>IFERROR(VLOOKUP($L39,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Diaria o por turno (verificación operativa) + inspección formal semanal documentada</v>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
@@ -6085,15 +6085,15 @@
       </c>
       <c r="K40" s="17">
         <f>IF(OR($I40="",$J40=""),"",$I40*$J40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="17">
+        <v>15</v>
+      </c>
+      <c r="L40" s="17" t="str">
         <f>IF($K40="","",IF($K40&gt;=20,"Extremo",IF($K40&gt;=12,"Alto",IF($K40&gt;=6,"Medio",IF($K40&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M40" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M40" s="8" t="str">
         <f>IFERROR(VLOOKUP($L40,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
@@ -6164,15 +6164,15 @@
       </c>
       <c r="K41" s="17">
         <f>IF(OR($I41="",$J41=""),"",$I41*$J41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="17">
+        <v>15</v>
+      </c>
+      <c r="L41" s="17" t="str">
         <f>IF($K41="","",IF($K41&gt;=20,"Extremo",IF($K41&gt;=12,"Alto",IF($K41&gt;=6,"Medio",IF($K41&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M41" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M41" s="8" t="str">
         <f>IFERROR(VLOOKUP($L41,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
@@ -6243,15 +6243,15 @@
       </c>
       <c r="K42" s="17">
         <f>IF(OR($I42="",$J42=""),"",$I42*$J42)</f>
-        <v/>
-      </c>
-      <c r="L42" s="17">
+        <v>15</v>
+      </c>
+      <c r="L42" s="17" t="str">
         <f>IF($K42="","",IF($K42&gt;=20,"Extremo",IF($K42&gt;=12,"Alto",IF($K42&gt;=6,"Medio",IF($K42&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M42" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M42" s="8" t="str">
         <f>IFERROR(VLOOKUP($L42,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
@@ -6322,15 +6322,15 @@
       </c>
       <c r="K43" s="17">
         <f>IF(OR($I43="",$J43=""),"",$I43*$J43)</f>
-        <v/>
-      </c>
-      <c r="L43" s="17">
+        <v>15</v>
+      </c>
+      <c r="L43" s="17" t="str">
         <f>IF($K43="","",IF($K43&gt;=20,"Extremo",IF($K43&gt;=12,"Alto",IF($K43&gt;=6,"Medio",IF($K43&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M43" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M43" s="8" t="str">
         <f>IFERROR(VLOOKUP($L43,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
@@ -6401,15 +6401,15 @@
       </c>
       <c r="K44" s="17">
         <f>IF(OR($I44="",$J44=""),"",$I44*$J44)</f>
-        <v/>
-      </c>
-      <c r="L44" s="17">
+        <v>10</v>
+      </c>
+      <c r="L44" s="17" t="str">
         <f>IF($K44="","",IF($K44&gt;=20,"Extremo",IF($K44&gt;=12,"Alto",IF($K44&gt;=6,"Medio",IF($K44&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M44" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M44" s="8" t="str">
         <f>IFERROR(VLOOKUP($L44,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
@@ -6480,15 +6480,15 @@
       </c>
       <c r="K45" s="17">
         <f>IF(OR($I45="",$J45=""),"",$I45*$J45)</f>
-        <v/>
-      </c>
-      <c r="L45" s="17">
+        <v>15</v>
+      </c>
+      <c r="L45" s="17" t="str">
         <f>IF($K45="","",IF($K45&gt;=20,"Extremo",IF($K45&gt;=12,"Alto",IF($K45&gt;=6,"Medio",IF($K45&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M45" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M45" s="8" t="str">
         <f>IFERROR(VLOOKUP($L45,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
@@ -6559,15 +6559,15 @@
       </c>
       <c r="K46" s="17">
         <f>IF(OR($I46="",$J46=""),"",$I46*$J46)</f>
-        <v/>
-      </c>
-      <c r="L46" s="17">
+        <v>15</v>
+      </c>
+      <c r="L46" s="17" t="str">
         <f>IF($K46="","",IF($K46&gt;=20,"Extremo",IF($K46&gt;=12,"Alto",IF($K46&gt;=6,"Medio",IF($K46&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M46" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M46" s="8" t="str">
         <f>IFERROR(VLOOKUP($L46,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
@@ -6638,15 +6638,15 @@
       </c>
       <c r="K47" s="17">
         <f>IF(OR($I47="",$J47=""),"",$I47*$J47)</f>
-        <v/>
-      </c>
-      <c r="L47" s="17">
+        <v>15</v>
+      </c>
+      <c r="L47" s="17" t="str">
         <f>IF($K47="","",IF($K47&gt;=20,"Extremo",IF($K47&gt;=12,"Alto",IF($K47&gt;=6,"Medio",IF($K47&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M47" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M47" s="8" t="str">
         <f>IFERROR(VLOOKUP($L47,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
@@ -6717,15 +6717,15 @@
       </c>
       <c r="K48" s="17">
         <f>IF(OR($I48="",$J48=""),"",$I48*$J48)</f>
-        <v/>
-      </c>
-      <c r="L48" s="17">
+        <v>10</v>
+      </c>
+      <c r="L48" s="17" t="str">
         <f>IF($K48="","",IF($K48&gt;=20,"Extremo",IF($K48&gt;=12,"Alto",IF($K48&gt;=6,"Medio",IF($K48&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M48" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M48" s="8" t="str">
         <f>IFERROR(VLOOKUP($L48,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
@@ -6796,15 +6796,15 @@
       </c>
       <c r="K49" s="17">
         <f>IF(OR($I49="",$J49=""),"",$I49*$J49)</f>
-        <v/>
-      </c>
-      <c r="L49" s="17">
+        <v>10</v>
+      </c>
+      <c r="L49" s="17" t="str">
         <f>IF($K49="","",IF($K49&gt;=20,"Extremo",IF($K49&gt;=12,"Alto",IF($K49&gt;=6,"Medio",IF($K49&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M49" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M49" s="8" t="str">
         <f>IFERROR(VLOOKUP($L49,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
@@ -6875,15 +6875,15 @@
       </c>
       <c r="K50" s="17">
         <f>IF(OR($I50="",$J50=""),"",$I50*$J50)</f>
-        <v/>
-      </c>
-      <c r="L50" s="17">
+        <v>15</v>
+      </c>
+      <c r="L50" s="17" t="str">
         <f>IF($K50="","",IF($K50&gt;=20,"Extremo",IF($K50&gt;=12,"Alto",IF($K50&gt;=6,"Medio",IF($K50&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M50" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M50" s="8" t="str">
         <f>IFERROR(VLOOKUP($L50,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
@@ -6954,15 +6954,15 @@
       </c>
       <c r="K51" s="17">
         <f>IF(OR($I51="",$J51=""),"",$I51*$J51)</f>
-        <v/>
-      </c>
-      <c r="L51" s="17">
+        <v>15</v>
+      </c>
+      <c r="L51" s="17" t="str">
         <f>IF($K51="","",IF($K51&gt;=20,"Extremo",IF($K51&gt;=12,"Alto",IF($K51&gt;=6,"Medio",IF($K51&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M51" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M51" s="8" t="str">
         <f>IFERROR(VLOOKUP($L51,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
@@ -7033,15 +7033,15 @@
       </c>
       <c r="K52" s="17">
         <f>IF(OR($I52="",$J52=""),"",$I52*$J52)</f>
-        <v/>
-      </c>
-      <c r="L52" s="17">
+        <v>12</v>
+      </c>
+      <c r="L52" s="17" t="str">
         <f>IF($K52="","",IF($K52&gt;=20,"Extremo",IF($K52&gt;=12,"Alto",IF($K52&gt;=6,"Medio",IF($K52&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M52" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M52" s="8" t="str">
         <f>IFERROR(VLOOKUP($L52,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
@@ -7112,15 +7112,15 @@
       </c>
       <c r="K53" s="17">
         <f>IF(OR($I53="",$J53=""),"",$I53*$J53)</f>
-        <v/>
-      </c>
-      <c r="L53" s="17">
+        <v>15</v>
+      </c>
+      <c r="L53" s="17" t="str">
         <f>IF($K53="","",IF($K53&gt;=20,"Extremo",IF($K53&gt;=12,"Alto",IF($K53&gt;=6,"Medio",IF($K53&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M53" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M53" s="8" t="str">
         <f>IFERROR(VLOOKUP($L53,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
@@ -7191,15 +7191,15 @@
       </c>
       <c r="K54" s="17">
         <f>IF(OR($I54="",$J54=""),"",$I54*$J54)</f>
-        <v/>
-      </c>
-      <c r="L54" s="17">
+        <v>15</v>
+      </c>
+      <c r="L54" s="17" t="str">
         <f>IF($K54="","",IF($K54&gt;=20,"Extremo",IF($K54&gt;=12,"Alto",IF($K54&gt;=6,"Medio",IF($K54&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M54" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M54" s="8" t="str">
         <f>IFERROR(VLOOKUP($L54,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
@@ -7270,15 +7270,15 @@
       </c>
       <c r="K55" s="17">
         <f>IF(OR($I55="",$J55=""),"",$I55*$J55)</f>
-        <v/>
-      </c>
-      <c r="L55" s="17">
+        <v>15</v>
+      </c>
+      <c r="L55" s="17" t="str">
         <f>IF($K55="","",IF($K55&gt;=20,"Extremo",IF($K55&gt;=12,"Alto",IF($K55&gt;=6,"Medio",IF($K55&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M55" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M55" s="8" t="str">
         <f>IFERROR(VLOOKUP($L55,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
@@ -7349,15 +7349,15 @@
       </c>
       <c r="K56" s="17">
         <f>IF(OR($I56="",$J56=""),"",$I56*$J56)</f>
-        <v/>
-      </c>
-      <c r="L56" s="17">
+        <v>16</v>
+      </c>
+      <c r="L56" s="17" t="str">
         <f>IF($K56="","",IF($K56&gt;=20,"Extremo",IF($K56&gt;=12,"Alto",IF($K56&gt;=6,"Medio",IF($K56&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M56" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M56" s="8" t="str">
         <f>IFERROR(VLOOKUP($L56,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
@@ -7428,15 +7428,15 @@
       </c>
       <c r="K57" s="17">
         <f>IF(OR($I57="",$J57=""),"",$I57*$J57)</f>
-        <v/>
-      </c>
-      <c r="L57" s="17">
+        <v>16</v>
+      </c>
+      <c r="L57" s="17" t="str">
         <f>IF($K57="","",IF($K57&gt;=20,"Extremo",IF($K57&gt;=12,"Alto",IF($K57&gt;=6,"Medio",IF($K57&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M57" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M57" s="8" t="str">
         <f>IFERROR(VLOOKUP($L57,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
@@ -7507,15 +7507,15 @@
       </c>
       <c r="K58" s="17">
         <f>IF(OR($I58="",$J58=""),"",$I58*$J58)</f>
-        <v/>
-      </c>
-      <c r="L58" s="17">
+        <v>15</v>
+      </c>
+      <c r="L58" s="17" t="str">
         <f>IF($K58="","",IF($K58&gt;=20,"Extremo",IF($K58&gt;=12,"Alto",IF($K58&gt;=6,"Medio",IF($K58&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M58" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M58" s="8" t="str">
         <f>IFERROR(VLOOKUP($L58,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
@@ -7586,15 +7586,15 @@
       </c>
       <c r="K59" s="17">
         <f>IF(OR($I59="",$J59=""),"",$I59*$J59)</f>
-        <v/>
-      </c>
-      <c r="L59" s="17">
+        <v>15</v>
+      </c>
+      <c r="L59" s="17" t="str">
         <f>IF($K59="","",IF($K59&gt;=20,"Extremo",IF($K59&gt;=12,"Alto",IF($K59&gt;=6,"Medio",IF($K59&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M59" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M59" s="8" t="str">
         <f>IFERROR(VLOOKUP($L59,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
@@ -7665,15 +7665,15 @@
       </c>
       <c r="K60" s="17">
         <f>IF(OR($I60="",$J60=""),"",$I60*$J60)</f>
-        <v/>
-      </c>
-      <c r="L60" s="17">
+        <v>12</v>
+      </c>
+      <c r="L60" s="17" t="str">
         <f>IF($K60="","",IF($K60&gt;=20,"Extremo",IF($K60&gt;=12,"Alto",IF($K60&gt;=6,"Medio",IF($K60&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M60" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M60" s="8" t="str">
         <f>IFERROR(VLOOKUP($L60,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
@@ -7744,15 +7744,15 @@
       </c>
       <c r="K61" s="17">
         <f>IF(OR($I61="",$J61=""),"",$I61*$J61)</f>
-        <v/>
-      </c>
-      <c r="L61" s="17">
+        <v>15</v>
+      </c>
+      <c r="L61" s="17" t="str">
         <f>IF($K61="","",IF($K61&gt;=20,"Extremo",IF($K61&gt;=12,"Alto",IF($K61&gt;=6,"Medio",IF($K61&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M61" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M61" s="8" t="str">
         <f>IFERROR(VLOOKUP($L61,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
@@ -7823,15 +7823,15 @@
       </c>
       <c r="K62" s="17">
         <f>IF(OR($I62="",$J62=""),"",$I62*$J62)</f>
-        <v/>
-      </c>
-      <c r="L62" s="17">
+        <v>10</v>
+      </c>
+      <c r="L62" s="17" t="str">
         <f>IF($K62="","",IF($K62&gt;=20,"Extremo",IF($K62&gt;=12,"Alto",IF($K62&gt;=6,"Medio",IF($K62&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M62" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M62" s="8" t="str">
         <f>IFERROR(VLOOKUP($L62,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
@@ -7902,15 +7902,15 @@
       </c>
       <c r="K63" s="17">
         <f>IF(OR($I63="",$J63=""),"",$I63*$J63)</f>
-        <v/>
-      </c>
-      <c r="L63" s="17">
+        <v>15</v>
+      </c>
+      <c r="L63" s="17" t="str">
         <f>IF($K63="","",IF($K63&gt;=20,"Extremo",IF($K63&gt;=12,"Alto",IF($K63&gt;=6,"Medio",IF($K63&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M63" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M63" s="8" t="str">
         <f>IFERROR(VLOOKUP($L63,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
@@ -7981,15 +7981,15 @@
       </c>
       <c r="K64" s="17">
         <f>IF(OR($I64="",$J64=""),"",$I64*$J64)</f>
-        <v/>
-      </c>
-      <c r="L64" s="17">
+        <v>15</v>
+      </c>
+      <c r="L64" s="17" t="str">
         <f>IF($K64="","",IF($K64&gt;=20,"Extremo",IF($K64&gt;=12,"Alto",IF($K64&gt;=6,"Medio",IF($K64&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M64" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M64" s="8" t="str">
         <f>IFERROR(VLOOKUP($L64,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
@@ -8060,15 +8060,15 @@
       </c>
       <c r="K65" s="17">
         <f>IF(OR($I65="",$J65=""),"",$I65*$J65)</f>
-        <v/>
-      </c>
-      <c r="L65" s="17">
+        <v>15</v>
+      </c>
+      <c r="L65" s="17" t="str">
         <f>IF($K65="","",IF($K65&gt;=20,"Extremo",IF($K65&gt;=12,"Alto",IF($K65&gt;=6,"Medio",IF($K65&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M65" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M65" s="8" t="str">
         <f>IFERROR(VLOOKUP($L65,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
@@ -8139,15 +8139,15 @@
       </c>
       <c r="K66" s="17">
         <f>IF(OR($I66="",$J66=""),"",$I66*$J66)</f>
-        <v/>
-      </c>
-      <c r="L66" s="17">
+        <v>10</v>
+      </c>
+      <c r="L66" s="17" t="str">
         <f>IF($K66="","",IF($K66&gt;=20,"Extremo",IF($K66&gt;=12,"Alto",IF($K66&gt;=6,"Medio",IF($K66&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M66" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M66" s="8" t="str">
         <f>IFERROR(VLOOKUP($L66,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
@@ -8218,15 +8218,15 @@
       </c>
       <c r="K67" s="17">
         <f>IF(OR($I67="",$J67=""),"",$I67*$J67)</f>
-        <v/>
-      </c>
-      <c r="L67" s="17">
+        <v>8</v>
+      </c>
+      <c r="L67" s="17" t="str">
         <f>IF($K67="","",IF($K67&gt;=20,"Extremo",IF($K67&gt;=12,"Alto",IF($K67&gt;=6,"Medio",IF($K67&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M67" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M67" s="8" t="str">
         <f>IFERROR(VLOOKUP($L67,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
@@ -8297,15 +8297,15 @@
       </c>
       <c r="K68" s="17">
         <f>IF(OR($I68="",$J68=""),"",$I68*$J68)</f>
-        <v/>
-      </c>
-      <c r="L68" s="17">
+        <v>8</v>
+      </c>
+      <c r="L68" s="17" t="str">
         <f>IF($K68="","",IF($K68&gt;=20,"Extremo",IF($K68&gt;=12,"Alto",IF($K68&gt;=6,"Medio",IF($K68&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M68" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M68" s="8" t="str">
         <f>IFERROR(VLOOKUP($L68,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
@@ -8376,15 +8376,15 @@
       </c>
       <c r="K69" s="17">
         <f>IF(OR($I69="",$J69=""),"",$I69*$J69)</f>
-        <v/>
-      </c>
-      <c r="L69" s="17">
+        <v>8</v>
+      </c>
+      <c r="L69" s="17" t="str">
         <f>IF($K69="","",IF($K69&gt;=20,"Extremo",IF($K69&gt;=12,"Alto",IF($K69&gt;=6,"Medio",IF($K69&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M69" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M69" s="8" t="str">
         <f>IFERROR(VLOOKUP($L69,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
@@ -8455,15 +8455,15 @@
       </c>
       <c r="K70" s="17">
         <f>IF(OR($I70="",$J70=""),"",$I70*$J70)</f>
-        <v/>
-      </c>
-      <c r="L70" s="17">
+        <v>15</v>
+      </c>
+      <c r="L70" s="17" t="str">
         <f>IF($K70="","",IF($K70&gt;=20,"Extremo",IF($K70&gt;=12,"Alto",IF($K70&gt;=6,"Medio",IF($K70&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M70" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M70" s="8" t="str">
         <f>IFERROR(VLOOKUP($L70,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
@@ -8534,15 +8534,15 @@
       </c>
       <c r="K71" s="17">
         <f>IF(OR($I71="",$J71=""),"",$I71*$J71)</f>
-        <v/>
-      </c>
-      <c r="L71" s="17">
+        <v>15</v>
+      </c>
+      <c r="L71" s="17" t="str">
         <f>IF($K71="","",IF($K71&gt;=20,"Extremo",IF($K71&gt;=12,"Alto",IF($K71&gt;=6,"Medio",IF($K71&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M71" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M71" s="8" t="str">
         <f>IFERROR(VLOOKUP($L71,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
@@ -8613,15 +8613,15 @@
       </c>
       <c r="K72" s="17">
         <f>IF(OR($I72="",$J72=""),"",$I72*$J72)</f>
-        <v/>
-      </c>
-      <c r="L72" s="17">
+        <v>10</v>
+      </c>
+      <c r="L72" s="17" t="str">
         <f>IF($K72="","",IF($K72&gt;=20,"Extremo",IF($K72&gt;=12,"Alto",IF($K72&gt;=6,"Medio",IF($K72&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M72" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M72" s="8" t="str">
         <f>IFERROR(VLOOKUP($L72,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
@@ -8692,15 +8692,15 @@
       </c>
       <c r="K73" s="17">
         <f>IF(OR($I73="",$J73=""),"",$I73*$J73)</f>
-        <v/>
-      </c>
-      <c r="L73" s="17">
+        <v>12</v>
+      </c>
+      <c r="L73" s="17" t="str">
         <f>IF($K73="","",IF($K73&gt;=20,"Extremo",IF($K73&gt;=12,"Alto",IF($K73&gt;=6,"Medio",IF($K73&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M73" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M73" s="8" t="str">
         <f>IFERROR(VLOOKUP($L73,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N73" s="8" t="inlineStr">
         <is>
@@ -8771,15 +8771,15 @@
       </c>
       <c r="K74" s="17">
         <f>IF(OR($I74="",$J74=""),"",$I74*$J74)</f>
-        <v/>
-      </c>
-      <c r="L74" s="17">
+        <v>10</v>
+      </c>
+      <c r="L74" s="17" t="str">
         <f>IF($K74="","",IF($K74&gt;=20,"Extremo",IF($K74&gt;=12,"Alto",IF($K74&gt;=6,"Medio",IF($K74&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M74" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M74" s="8" t="str">
         <f>IFERROR(VLOOKUP($L74,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
@@ -8850,15 +8850,15 @@
       </c>
       <c r="K75" s="17">
         <f>IF(OR($I75="",$J75=""),"",$I75*$J75)</f>
-        <v/>
-      </c>
-      <c r="L75" s="17">
+        <v>6</v>
+      </c>
+      <c r="L75" s="17" t="str">
         <f>IF($K75="","",IF($K75&gt;=20,"Extremo",IF($K75&gt;=12,"Alto",IF($K75&gt;=6,"Medio",IF($K75&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M75" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M75" s="8" t="str">
         <f>IFERROR(VLOOKUP($L75,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
@@ -8929,15 +8929,15 @@
       </c>
       <c r="K76" s="17">
         <f>IF(OR($I76="",$J76=""),"",$I76*$J76)</f>
-        <v/>
-      </c>
-      <c r="L76" s="17">
+        <v>16</v>
+      </c>
+      <c r="L76" s="17" t="str">
         <f>IF($K76="","",IF($K76&gt;=20,"Extremo",IF($K76&gt;=12,"Alto",IF($K76&gt;=6,"Medio",IF($K76&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M76" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M76" s="8" t="str">
         <f>IFERROR(VLOOKUP($L76,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
@@ -9008,15 +9008,15 @@
       </c>
       <c r="K77" s="17">
         <f>IF(OR($I77="",$J77=""),"",$I77*$J77)</f>
-        <v/>
-      </c>
-      <c r="L77" s="17">
+        <v>10</v>
+      </c>
+      <c r="L77" s="17" t="str">
         <f>IF($K77="","",IF($K77&gt;=20,"Extremo",IF($K77&gt;=12,"Alto",IF($K77&gt;=6,"Medio",IF($K77&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M77" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M77" s="8" t="str">
         <f>IFERROR(VLOOKUP($L77,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
@@ -9087,15 +9087,15 @@
       </c>
       <c r="K78" s="17">
         <f>IF(OR($I78="",$J78=""),"",$I78*$J78)</f>
-        <v/>
-      </c>
-      <c r="L78" s="17">
+        <v>12</v>
+      </c>
+      <c r="L78" s="17" t="str">
         <f>IF($K78="","",IF($K78&gt;=20,"Extremo",IF($K78&gt;=12,"Alto",IF($K78&gt;=6,"Medio",IF($K78&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M78" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M78" s="8" t="str">
         <f>IFERROR(VLOOKUP($L78,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
@@ -9166,15 +9166,15 @@
       </c>
       <c r="K79" s="17">
         <f>IF(OR($I79="",$J79=""),"",$I79*$J79)</f>
-        <v/>
-      </c>
-      <c r="L79" s="17">
+        <v>12</v>
+      </c>
+      <c r="L79" s="17" t="str">
         <f>IF($K79="","",IF($K79&gt;=20,"Extremo",IF($K79&gt;=12,"Alto",IF($K79&gt;=6,"Medio",IF($K79&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M79" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M79" s="8" t="str">
         <f>IFERROR(VLOOKUP($L79,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
@@ -9245,15 +9245,15 @@
       </c>
       <c r="K80" s="17">
         <f>IF(OR($I80="",$J80=""),"",$I80*$J80)</f>
-        <v/>
-      </c>
-      <c r="L80" s="17">
+        <v>10</v>
+      </c>
+      <c r="L80" s="17" t="str">
         <f>IF($K80="","",IF($K80&gt;=20,"Extremo",IF($K80&gt;=12,"Alto",IF($K80&gt;=6,"Medio",IF($K80&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M80" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M80" s="8" t="str">
         <f>IFERROR(VLOOKUP($L80,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
@@ -9324,15 +9324,15 @@
       </c>
       <c r="K81" s="17">
         <f>IF(OR($I81="",$J81=""),"",$I81*$J81)</f>
-        <v/>
-      </c>
-      <c r="L81" s="17">
+        <v>12</v>
+      </c>
+      <c r="L81" s="17" t="str">
         <f>IF($K81="","",IF($K81&gt;=20,"Extremo",IF($K81&gt;=12,"Alto",IF($K81&gt;=6,"Medio",IF($K81&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M81" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M81" s="8" t="str">
         <f>IFERROR(VLOOKUP($L81,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
@@ -9403,15 +9403,15 @@
       </c>
       <c r="K82" s="17">
         <f>IF(OR($I82="",$J82=""),"",$I82*$J82)</f>
-        <v/>
-      </c>
-      <c r="L82" s="17">
+        <v>12</v>
+      </c>
+      <c r="L82" s="17" t="str">
         <f>IF($K82="","",IF($K82&gt;=20,"Extremo",IF($K82&gt;=12,"Alto",IF($K82&gt;=6,"Medio",IF($K82&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M82" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M82" s="8" t="str">
         <f>IFERROR(VLOOKUP($L82,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
@@ -9482,15 +9482,15 @@
       </c>
       <c r="K83" s="17">
         <f>IF(OR($I83="",$J83=""),"",$I83*$J83)</f>
-        <v/>
-      </c>
-      <c r="L83" s="17">
+        <v>10</v>
+      </c>
+      <c r="L83" s="17" t="str">
         <f>IF($K83="","",IF($K83&gt;=20,"Extremo",IF($K83&gt;=12,"Alto",IF($K83&gt;=6,"Medio",IF($K83&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M83" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M83" s="8" t="str">
         <f>IFERROR(VLOOKUP($L83,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
@@ -9561,15 +9561,15 @@
       </c>
       <c r="K84" s="17">
         <f>IF(OR($I84="",$J84=""),"",$I84*$J84)</f>
-        <v/>
-      </c>
-      <c r="L84" s="17">
+        <v>15</v>
+      </c>
+      <c r="L84" s="17" t="str">
         <f>IF($K84="","",IF($K84&gt;=20,"Extremo",IF($K84&gt;=12,"Alto",IF($K84&gt;=6,"Medio",IF($K84&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M84" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M84" s="8" t="str">
         <f>IFERROR(VLOOKUP($L84,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
@@ -9640,15 +9640,15 @@
       </c>
       <c r="K85" s="17">
         <f>IF(OR($I85="",$J85=""),"",$I85*$J85)</f>
-        <v/>
-      </c>
-      <c r="L85" s="17">
+        <v>15</v>
+      </c>
+      <c r="L85" s="17" t="str">
         <f>IF($K85="","",IF($K85&gt;=20,"Extremo",IF($K85&gt;=12,"Alto",IF($K85&gt;=6,"Medio",IF($K85&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M85" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M85" s="8" t="str">
         <f>IFERROR(VLOOKUP($L85,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N85" s="8" t="inlineStr">
         <is>
@@ -9719,15 +9719,15 @@
       </c>
       <c r="K86" s="17">
         <f>IF(OR($I86="",$J86=""),"",$I86*$J86)</f>
-        <v/>
-      </c>
-      <c r="L86" s="17">
+        <v>9</v>
+      </c>
+      <c r="L86" s="17" t="str">
         <f>IF($K86="","",IF($K86&gt;=20,"Extremo",IF($K86&gt;=12,"Alto",IF($K86&gt;=6,"Medio",IF($K86&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M86" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M86" s="8" t="str">
         <f>IFERROR(VLOOKUP($L86,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N86" s="8" t="inlineStr">
         <is>
@@ -9798,15 +9798,15 @@
       </c>
       <c r="K87" s="17">
         <f>IF(OR($I87="",$J87=""),"",$I87*$J87)</f>
-        <v/>
-      </c>
-      <c r="L87" s="17">
+        <v>12</v>
+      </c>
+      <c r="L87" s="17" t="str">
         <f>IF($K87="","",IF($K87&gt;=20,"Extremo",IF($K87&gt;=12,"Alto",IF($K87&gt;=6,"Medio",IF($K87&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M87" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M87" s="8" t="str">
         <f>IFERROR(VLOOKUP($L87,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N87" s="8" t="inlineStr">
         <is>
@@ -9877,15 +9877,15 @@
       </c>
       <c r="K88" s="17">
         <f>IF(OR($I88="",$J88=""),"",$I88*$J88)</f>
-        <v/>
-      </c>
-      <c r="L88" s="17">
+        <v>12</v>
+      </c>
+      <c r="L88" s="17" t="str">
         <f>IF($K88="","",IF($K88&gt;=20,"Extremo",IF($K88&gt;=12,"Alto",IF($K88&gt;=6,"Medio",IF($K88&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M88" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M88" s="8" t="str">
         <f>IFERROR(VLOOKUP($L88,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N88" s="8" t="inlineStr">
         <is>
@@ -9956,15 +9956,15 @@
       </c>
       <c r="K89" s="17">
         <f>IF(OR($I89="",$J89=""),"",$I89*$J89)</f>
-        <v/>
-      </c>
-      <c r="L89" s="17">
+        <v>12</v>
+      </c>
+      <c r="L89" s="17" t="str">
         <f>IF($K89="","",IF($K89&gt;=20,"Extremo",IF($K89&gt;=12,"Alto",IF($K89&gt;=6,"Medio",IF($K89&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M89" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M89" s="8" t="str">
         <f>IFERROR(VLOOKUP($L89,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N89" s="8" t="inlineStr">
         <is>
@@ -10035,15 +10035,15 @@
       </c>
       <c r="K90" s="17">
         <f>IF(OR($I90="",$J90=""),"",$I90*$J90)</f>
-        <v/>
-      </c>
-      <c r="L90" s="17">
+        <v>15</v>
+      </c>
+      <c r="L90" s="17" t="str">
         <f>IF($K90="","",IF($K90&gt;=20,"Extremo",IF($K90&gt;=12,"Alto",IF($K90&gt;=6,"Medio",IF($K90&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M90" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M90" s="8" t="str">
         <f>IFERROR(VLOOKUP($L90,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N90" s="8" t="inlineStr">
         <is>
@@ -10114,15 +10114,15 @@
       </c>
       <c r="K91" s="17">
         <f>IF(OR($I91="",$J91=""),"",$I91*$J91)</f>
-        <v/>
-      </c>
-      <c r="L91" s="17">
+        <v>9</v>
+      </c>
+      <c r="L91" s="17" t="str">
         <f>IF($K91="","",IF($K91&gt;=20,"Extremo",IF($K91&gt;=12,"Alto",IF($K91&gt;=6,"Medio",IF($K91&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M91" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M91" s="8" t="str">
         <f>IFERROR(VLOOKUP($L91,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N91" s="8" t="inlineStr">
         <is>
@@ -10193,15 +10193,15 @@
       </c>
       <c r="K92" s="17">
         <f>IF(OR($I92="",$J92=""),"",$I92*$J92)</f>
-        <v/>
-      </c>
-      <c r="L92" s="17">
+        <v>9</v>
+      </c>
+      <c r="L92" s="17" t="str">
         <f>IF($K92="","",IF($K92&gt;=20,"Extremo",IF($K92&gt;=12,"Alto",IF($K92&gt;=6,"Medio",IF($K92&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M92" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M92" s="8" t="str">
         <f>IFERROR(VLOOKUP($L92,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N92" s="8" t="inlineStr">
         <is>
@@ -10272,15 +10272,15 @@
       </c>
       <c r="K93" s="17">
         <f>IF(OR($I93="",$J93=""),"",$I93*$J93)</f>
-        <v/>
-      </c>
-      <c r="L93" s="17">
+        <v>16</v>
+      </c>
+      <c r="L93" s="17" t="str">
         <f>IF($K93="","",IF($K93&gt;=20,"Extremo",IF($K93&gt;=12,"Alto",IF($K93&gt;=6,"Medio",IF($K93&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M93" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M93" s="8" t="str">
         <f>IFERROR(VLOOKUP($L93,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N93" s="8" t="inlineStr">
         <is>
@@ -10351,15 +10351,15 @@
       </c>
       <c r="K94" s="17">
         <f>IF(OR($I94="",$J94=""),"",$I94*$J94)</f>
-        <v/>
-      </c>
-      <c r="L94" s="17">
+        <v>9</v>
+      </c>
+      <c r="L94" s="17" t="str">
         <f>IF($K94="","",IF($K94&gt;=20,"Extremo",IF($K94&gt;=12,"Alto",IF($K94&gt;=6,"Medio",IF($K94&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M94" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M94" s="8" t="str">
         <f>IFERROR(VLOOKUP($L94,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N94" s="8" t="inlineStr">
         <is>
@@ -10430,15 +10430,15 @@
       </c>
       <c r="K95" s="17">
         <f>IF(OR($I95="",$J95=""),"",$I95*$J95)</f>
-        <v/>
-      </c>
-      <c r="L95" s="17">
+        <v>10</v>
+      </c>
+      <c r="L95" s="17" t="str">
         <f>IF($K95="","",IF($K95&gt;=20,"Extremo",IF($K95&gt;=12,"Alto",IF($K95&gt;=6,"Medio",IF($K95&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M95" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M95" s="8" t="str">
         <f>IFERROR(VLOOKUP($L95,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N95" s="8" t="inlineStr">
         <is>
@@ -10509,15 +10509,15 @@
       </c>
       <c r="K96" s="17">
         <f>IF(OR($I96="",$J96=""),"",$I96*$J96)</f>
-        <v/>
-      </c>
-      <c r="L96" s="17">
+        <v>12</v>
+      </c>
+      <c r="L96" s="17" t="str">
         <f>IF($K96="","",IF($K96&gt;=20,"Extremo",IF($K96&gt;=12,"Alto",IF($K96&gt;=6,"Medio",IF($K96&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M96" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M96" s="8" t="str">
         <f>IFERROR(VLOOKUP($L96,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N96" s="8" t="inlineStr">
         <is>
@@ -10588,15 +10588,15 @@
       </c>
       <c r="K97" s="17">
         <f>IF(OR($I97="",$J97=""),"",$I97*$J97)</f>
-        <v/>
-      </c>
-      <c r="L97" s="17">
+        <v>15</v>
+      </c>
+      <c r="L97" s="17" t="str">
         <f>IF($K97="","",IF($K97&gt;=20,"Extremo",IF($K97&gt;=12,"Alto",IF($K97&gt;=6,"Medio",IF($K97&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M97" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M97" s="8" t="str">
         <f>IFERROR(VLOOKUP($L97,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N97" s="8" t="inlineStr">
         <is>
@@ -10667,15 +10667,15 @@
       </c>
       <c r="K98" s="17">
         <f>IF(OR($I98="",$J98=""),"",$I98*$J98)</f>
-        <v/>
-      </c>
-      <c r="L98" s="17">
+        <v>12</v>
+      </c>
+      <c r="L98" s="17" t="str">
         <f>IF($K98="","",IF($K98&gt;=20,"Extremo",IF($K98&gt;=12,"Alto",IF($K98&gt;=6,"Medio",IF($K98&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M98" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M98" s="8" t="str">
         <f>IFERROR(VLOOKUP($L98,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N98" s="8" t="inlineStr">
         <is>
@@ -10746,15 +10746,15 @@
       </c>
       <c r="K99" s="17">
         <f>IF(OR($I99="",$J99=""),"",$I99*$J99)</f>
-        <v/>
-      </c>
-      <c r="L99" s="17">
+        <v>15</v>
+      </c>
+      <c r="L99" s="17" t="str">
         <f>IF($K99="","",IF($K99&gt;=20,"Extremo",IF($K99&gt;=12,"Alto",IF($K99&gt;=6,"Medio",IF($K99&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M99" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M99" s="8" t="str">
         <f>IFERROR(VLOOKUP($L99,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N99" s="8" t="inlineStr">
         <is>
@@ -10825,15 +10825,15 @@
       </c>
       <c r="K100" s="17">
         <f>IF(OR($I100="",$J100=""),"",$I100*$J100)</f>
-        <v/>
-      </c>
-      <c r="L100" s="17">
+        <v>12</v>
+      </c>
+      <c r="L100" s="17" t="str">
         <f>IF($K100="","",IF($K100&gt;=20,"Extremo",IF($K100&gt;=12,"Alto",IF($K100&gt;=6,"Medio",IF($K100&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M100" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M100" s="8" t="str">
         <f>IFERROR(VLOOKUP($L100,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N100" s="8" t="inlineStr">
         <is>
@@ -10904,15 +10904,15 @@
       </c>
       <c r="K101" s="17">
         <f>IF(OR($I101="",$J101=""),"",$I101*$J101)</f>
-        <v/>
-      </c>
-      <c r="L101" s="17">
+        <v>15</v>
+      </c>
+      <c r="L101" s="17" t="str">
         <f>IF($K101="","",IF($K101&gt;=20,"Extremo",IF($K101&gt;=12,"Alto",IF($K101&gt;=6,"Medio",IF($K101&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M101" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M101" s="8" t="str">
         <f>IFERROR(VLOOKUP($L101,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N101" s="8" t="inlineStr">
         <is>
@@ -10983,15 +10983,15 @@
       </c>
       <c r="K102" s="17">
         <f>IF(OR($I102="",$J102=""),"",$I102*$J102)</f>
-        <v/>
-      </c>
-      <c r="L102" s="17">
+        <v>9</v>
+      </c>
+      <c r="L102" s="17" t="str">
         <f>IF($K102="","",IF($K102&gt;=20,"Extremo",IF($K102&gt;=12,"Alto",IF($K102&gt;=6,"Medio",IF($K102&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M102" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M102" s="8" t="str">
         <f>IFERROR(VLOOKUP($L102,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N102" s="8" t="inlineStr">
         <is>
@@ -11062,15 +11062,15 @@
       </c>
       <c r="K103" s="17">
         <f>IF(OR($I103="",$J103=""),"",$I103*$J103)</f>
-        <v/>
-      </c>
-      <c r="L103" s="17">
+        <v>12</v>
+      </c>
+      <c r="L103" s="17" t="str">
         <f>IF($K103="","",IF($K103&gt;=20,"Extremo",IF($K103&gt;=12,"Alto",IF($K103&gt;=6,"Medio",IF($K103&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M103" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M103" s="8" t="str">
         <f>IFERROR(VLOOKUP($L103,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N103" s="8" t="inlineStr">
         <is>
@@ -11141,15 +11141,15 @@
       </c>
       <c r="K104" s="17">
         <f>IF(OR($I104="",$J104=""),"",$I104*$J104)</f>
-        <v/>
-      </c>
-      <c r="L104" s="17">
+        <v>12</v>
+      </c>
+      <c r="L104" s="17" t="str">
         <f>IF($K104="","",IF($K104&gt;=20,"Extremo",IF($K104&gt;=12,"Alto",IF($K104&gt;=6,"Medio",IF($K104&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M104" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M104" s="8" t="str">
         <f>IFERROR(VLOOKUP($L104,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N104" s="8" t="inlineStr">
         <is>
@@ -11220,15 +11220,15 @@
       </c>
       <c r="K105" s="17">
         <f>IF(OR($I105="",$J105=""),"",$I105*$J105)</f>
-        <v/>
-      </c>
-      <c r="L105" s="17">
+        <v>9</v>
+      </c>
+      <c r="L105" s="17" t="str">
         <f>IF($K105="","",IF($K105&gt;=20,"Extremo",IF($K105&gt;=12,"Alto",IF($K105&gt;=6,"Medio",IF($K105&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M105" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M105" s="8" t="str">
         <f>IFERROR(VLOOKUP($L105,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N105" s="8" t="inlineStr">
         <is>
@@ -11299,15 +11299,15 @@
       </c>
       <c r="K106" s="17">
         <f>IF(OR($I106="",$J106=""),"",$I106*$J106)</f>
-        <v/>
-      </c>
-      <c r="L106" s="17">
+        <v>10</v>
+      </c>
+      <c r="L106" s="17" t="str">
         <f>IF($K106="","",IF($K106&gt;=20,"Extremo",IF($K106&gt;=12,"Alto",IF($K106&gt;=6,"Medio",IF($K106&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M106" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M106" s="8" t="str">
         <f>IFERROR(VLOOKUP($L106,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N106" s="8" t="inlineStr">
         <is>
@@ -11378,15 +11378,15 @@
       </c>
       <c r="K107" s="17">
         <f>IF(OR($I107="",$J107=""),"",$I107*$J107)</f>
-        <v/>
-      </c>
-      <c r="L107" s="17">
+        <v>12</v>
+      </c>
+      <c r="L107" s="17" t="str">
         <f>IF($K107="","",IF($K107&gt;=20,"Extremo",IF($K107&gt;=12,"Alto",IF($K107&gt;=6,"Medio",IF($K107&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M107" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M107" s="8" t="str">
         <f>IFERROR(VLOOKUP($L107,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N107" s="8" t="inlineStr">
         <is>
@@ -11457,15 +11457,15 @@
       </c>
       <c r="K108" s="17">
         <f>IF(OR($I108="",$J108=""),"",$I108*$J108)</f>
-        <v/>
-      </c>
-      <c r="L108" s="17">
+        <v>9</v>
+      </c>
+      <c r="L108" s="17" t="str">
         <f>IF($K108="","",IF($K108&gt;=20,"Extremo",IF($K108&gt;=12,"Alto",IF($K108&gt;=6,"Medio",IF($K108&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M108" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M108" s="8" t="str">
         <f>IFERROR(VLOOKUP($L108,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N108" s="8" t="inlineStr">
         <is>
@@ -11536,15 +11536,15 @@
       </c>
       <c r="K109" s="17">
         <f>IF(OR($I109="",$J109=""),"",$I109*$J109)</f>
-        <v/>
-      </c>
-      <c r="L109" s="17">
+        <v>9</v>
+      </c>
+      <c r="L109" s="17" t="str">
         <f>IF($K109="","",IF($K109&gt;=20,"Extremo",IF($K109&gt;=12,"Alto",IF($K109&gt;=6,"Medio",IF($K109&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M109" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M109" s="8" t="str">
         <f>IFERROR(VLOOKUP($L109,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N109" s="8" t="inlineStr">
         <is>
@@ -11615,15 +11615,15 @@
       </c>
       <c r="K110" s="17">
         <f>IF(OR($I110="",$J110=""),"",$I110*$J110)</f>
-        <v/>
-      </c>
-      <c r="L110" s="17">
+        <v>9</v>
+      </c>
+      <c r="L110" s="17" t="str">
         <f>IF($K110="","",IF($K110&gt;=20,"Extremo",IF($K110&gt;=12,"Alto",IF($K110&gt;=6,"Medio",IF($K110&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M110" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M110" s="8" t="str">
         <f>IFERROR(VLOOKUP($L110,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N110" s="8" t="inlineStr">
         <is>
@@ -11694,15 +11694,15 @@
       </c>
       <c r="K111" s="17">
         <f>IF(OR($I111="",$J111=""),"",$I111*$J111)</f>
-        <v/>
-      </c>
-      <c r="L111" s="17">
+        <v>9</v>
+      </c>
+      <c r="L111" s="17" t="str">
         <f>IF($K111="","",IF($K111&gt;=20,"Extremo",IF($K111&gt;=12,"Alto",IF($K111&gt;=6,"Medio",IF($K111&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M111" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M111" s="8" t="str">
         <f>IFERROR(VLOOKUP($L111,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N111" s="8" t="inlineStr">
         <is>
@@ -11773,15 +11773,15 @@
       </c>
       <c r="K112" s="17">
         <f>IF(OR($I112="",$J112=""),"",$I112*$J112)</f>
-        <v/>
-      </c>
-      <c r="L112" s="17">
+        <v>15</v>
+      </c>
+      <c r="L112" s="17" t="str">
         <f>IF($K112="","",IF($K112&gt;=20,"Extremo",IF($K112&gt;=12,"Alto",IF($K112&gt;=6,"Medio",IF($K112&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M112" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M112" s="8" t="str">
         <f>IFERROR(VLOOKUP($L112,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N112" s="8" t="inlineStr">
         <is>
@@ -11852,15 +11852,15 @@
       </c>
       <c r="K113" s="17">
         <f>IF(OR($I113="",$J113=""),"",$I113*$J113)</f>
-        <v/>
-      </c>
-      <c r="L113" s="17">
+        <v>10</v>
+      </c>
+      <c r="L113" s="17" t="str">
         <f>IF($K113="","",IF($K113&gt;=20,"Extremo",IF($K113&gt;=12,"Alto",IF($K113&gt;=6,"Medio",IF($K113&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M113" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M113" s="8" t="str">
         <f>IFERROR(VLOOKUP($L113,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N113" s="8" t="inlineStr">
         <is>
@@ -11931,15 +11931,15 @@
       </c>
       <c r="K114" s="17">
         <f>IF(OR($I114="",$J114=""),"",$I114*$J114)</f>
-        <v/>
-      </c>
-      <c r="L114" s="17">
+        <v>12</v>
+      </c>
+      <c r="L114" s="17" t="str">
         <f>IF($K114="","",IF($K114&gt;=20,"Extremo",IF($K114&gt;=12,"Alto",IF($K114&gt;=6,"Medio",IF($K114&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M114" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M114" s="8" t="str">
         <f>IFERROR(VLOOKUP($L114,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N114" s="8" t="inlineStr">
         <is>
@@ -12010,15 +12010,15 @@
       </c>
       <c r="K115" s="17">
         <f>IF(OR($I115="",$J115=""),"",$I115*$J115)</f>
-        <v/>
-      </c>
-      <c r="L115" s="17">
+        <v>12</v>
+      </c>
+      <c r="L115" s="17" t="str">
         <f>IF($K115="","",IF($K115&gt;=20,"Extremo",IF($K115&gt;=12,"Alto",IF($K115&gt;=6,"Medio",IF($K115&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M115" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M115" s="8" t="str">
         <f>IFERROR(VLOOKUP($L115,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N115" s="8" t="inlineStr">
         <is>
@@ -12089,15 +12089,15 @@
       </c>
       <c r="K116" s="17">
         <f>IF(OR($I116="",$J116=""),"",$I116*$J116)</f>
-        <v/>
-      </c>
-      <c r="L116" s="17">
+        <v>10</v>
+      </c>
+      <c r="L116" s="17" t="str">
         <f>IF($K116="","",IF($K116&gt;=20,"Extremo",IF($K116&gt;=12,"Alto",IF($K116&gt;=6,"Medio",IF($K116&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M116" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M116" s="8" t="str">
         <f>IFERROR(VLOOKUP($L116,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N116" s="8" t="inlineStr">
         <is>
@@ -12168,15 +12168,15 @@
       </c>
       <c r="K117" s="17">
         <f>IF(OR($I117="",$J117=""),"",$I117*$J117)</f>
-        <v/>
-      </c>
-      <c r="L117" s="17">
+        <v>10</v>
+      </c>
+      <c r="L117" s="17" t="str">
         <f>IF($K117="","",IF($K117&gt;=20,"Extremo",IF($K117&gt;=12,"Alto",IF($K117&gt;=6,"Medio",IF($K117&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M117" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M117" s="8" t="str">
         <f>IFERROR(VLOOKUP($L117,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N117" s="8" t="inlineStr">
         <is>
@@ -12247,15 +12247,15 @@
       </c>
       <c r="K118" s="17">
         <f>IF(OR($I118="",$J118=""),"",$I118*$J118)</f>
-        <v/>
-      </c>
-      <c r="L118" s="17">
+        <v>12</v>
+      </c>
+      <c r="L118" s="17" t="str">
         <f>IF($K118="","",IF($K118&gt;=20,"Extremo",IF($K118&gt;=12,"Alto",IF($K118&gt;=6,"Medio",IF($K118&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M118" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M118" s="8" t="str">
         <f>IFERROR(VLOOKUP($L118,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N118" s="8" t="inlineStr">
         <is>
@@ -12326,15 +12326,15 @@
       </c>
       <c r="K119" s="17">
         <f>IF(OR($I119="",$J119=""),"",$I119*$J119)</f>
-        <v/>
-      </c>
-      <c r="L119" s="17">
+        <v>15</v>
+      </c>
+      <c r="L119" s="17" t="str">
         <f>IF($K119="","",IF($K119&gt;=20,"Extremo",IF($K119&gt;=12,"Alto",IF($K119&gt;=6,"Medio",IF($K119&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M119" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M119" s="8" t="str">
         <f>IFERROR(VLOOKUP($L119,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N119" s="8" t="inlineStr">
         <is>
@@ -12405,15 +12405,15 @@
       </c>
       <c r="K120" s="17">
         <f>IF(OR($I120="",$J120=""),"",$I120*$J120)</f>
-        <v/>
-      </c>
-      <c r="L120" s="17">
+        <v>10</v>
+      </c>
+      <c r="L120" s="17" t="str">
         <f>IF($K120="","",IF($K120&gt;=20,"Extremo",IF($K120&gt;=12,"Alto",IF($K120&gt;=6,"Medio",IF($K120&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M120" s="8">
+        <v>Medio</v>
+      </c>
+      <c r="M120" s="8" t="str">
         <f>IFERROR(VLOOKUP($L120,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Mensual para elementos operativos; trimestral para elementos estructurales o de instalación</v>
       </c>
       <c r="N120" s="8" t="inlineStr">
         <is>
@@ -12484,15 +12484,15 @@
       </c>
       <c r="K121" s="17">
         <f>IF(OR($I121="",$J121=""),"",$I121*$J121)</f>
-        <v/>
-      </c>
-      <c r="L121" s="17">
+        <v>12</v>
+      </c>
+      <c r="L121" s="17" t="str">
         <f>IF($K121="","",IF($K121&gt;=20,"Extremo",IF($K121&gt;=12,"Alto",IF($K121&gt;=6,"Medio",IF($K121&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M121" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M121" s="8" t="str">
         <f>IFERROR(VLOOKUP($L121,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N121" s="8" t="inlineStr">
         <is>
@@ -12563,15 +12563,15 @@
       </c>
       <c r="K122" s="17">
         <f>IF(OR($I122="",$J122=""),"",$I122*$J122)</f>
-        <v/>
-      </c>
-      <c r="L122" s="17">
+        <v>12</v>
+      </c>
+      <c r="L122" s="17" t="str">
         <f>IF($K122="","",IF($K122&gt;=20,"Extremo",IF($K122&gt;=12,"Alto",IF($K122&gt;=6,"Medio",IF($K122&gt;=3,"Bajo","Muy bajo")))))</f>
-        <v/>
-      </c>
-      <c r="M122" s="8">
+        <v>Alto</v>
+      </c>
+      <c r="M122" s="8" t="str">
         <f>IFERROR(VLOOKUP($L122,'3. Escalas y Criterios'!$A$30:$C$34,3,FALSE),"")</f>
-        <v/>
+        <v>Semanal (verificación) + inspección formal mensual documentada</v>
       </c>
       <c r="N122" s="8" t="inlineStr">
         <is>
@@ -18607,11 +18607,11 @@
       </c>
       <c r="C6" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D6" s="47">
         <f>IFERROR(C6/$C$11,0)</f>
-        <v/>
+        <v>0.0423728813559322</v>
       </c>
       <c r="E6" s="48" t="inlineStr">
         <is>
@@ -18631,11 +18631,11 @@
       </c>
       <c r="C7" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="D7" s="47">
         <f>IFERROR(C7/$C$11,0)</f>
-        <v/>
+        <v>0.635593220338983</v>
       </c>
       <c r="E7" s="48" t="inlineStr">
         <is>
@@ -18655,11 +18655,11 @@
       </c>
       <c r="C8" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="D8" s="47">
         <f>IFERROR(C8/$C$11,0)</f>
-        <v/>
+        <v>0.3220338983050847</v>
       </c>
       <c r="E8" s="48" t="inlineStr">
         <is>
@@ -18679,11 +18679,11 @@
       </c>
       <c r="C9" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D9" s="47">
         <f>IFERROR(C9/$C$11,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="48" t="inlineStr">
         <is>
@@ -18703,11 +18703,11 @@
       </c>
       <c r="C10" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D10" s="47">
         <f>IFERROR(C10/$C$11,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="48" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="C11" s="50">
         <f>SUM(C6:C10)</f>
-        <v/>
+        <v>118</v>
       </c>
       <c r="D11" s="51" t="n"/>
     </row>
@@ -18769,11 +18769,11 @@
       </c>
       <c r="C15" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$Q$5:$Q$122,"Sí")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D15" s="47">
         <f>IFERROR(C15/COUNTA('2. Matriz de Riesgos'!$Q$5:$Q$122),0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -18784,11 +18784,11 @@
       </c>
       <c r="C16" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$Q$5:$Q$122,"Parcial")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D16" s="47">
         <f>IFERROR(C16/COUNTA('2. Matriz de Riesgos'!$Q$5:$Q$122),0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -18799,11 +18799,11 @@
       </c>
       <c r="C17" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$Q$5:$Q$122,"No")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D17" s="47">
         <f>IFERROR(C17/COUNTA('2. Matriz de Riesgos'!$Q$5:$Q$122),0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -18814,11 +18814,11 @@
       </c>
       <c r="C18" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$Q$5:$Q$122,"N.A.")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D18" s="47">
         <f>IFERROR(C18/COUNTA('2. Matriz de Riesgos'!$Q$5:$Q$122),0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -18829,11 +18829,11 @@
       </c>
       <c r="C19" s="46">
         <f>COUNTIF('2. Matriz de Riesgos'!$Q$5:$Q$122,"Sin evaluar")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D19" s="47">
         <f>IFERROR(C19/COUNTA('2. Matriz de Riesgos'!$Q$5:$Q$122),0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="C20" s="52">
         <f>IFERROR(C15/(C15+C16+C17),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D20" s="51" t="n"/>
     </row>
@@ -18906,31 +18906,31 @@
       </c>
       <c r="C24" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B24,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D24" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B24,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E24" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B24,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F24" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B24,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G24" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B24,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H24" s="17">
         <f>SUM(C24:G24)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I24" s="46">
         <f>C24+D24</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
@@ -18941,31 +18941,31 @@
       </c>
       <c r="C25" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B25,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D25" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B25,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="E25" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B25,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F25" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B25,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B25,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H25" s="17">
         <f>SUM(C25:G25)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="I25" s="46">
         <f>C25+D25</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -18976,31 +18976,31 @@
       </c>
       <c r="C26" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B26,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D26" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B26,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="E26" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B26,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F26" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B26,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G26" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B26,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H26" s="17">
         <f>SUM(C26:G26)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I26" s="46">
         <f>C26+D26</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -19011,31 +19011,31 @@
       </c>
       <c r="C27" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B27,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D27" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B27,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="E27" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B27,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F27" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B27,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G27" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B27,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H27" s="17">
         <f>SUM(C27:G27)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I27" s="46">
         <f>C27+D27</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -19046,31 +19046,31 @@
       </c>
       <c r="C28" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B28,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D28" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B28,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="E28" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B28,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F28" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B28,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G28" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B28,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H28" s="17">
         <f>SUM(C28:G28)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I28" s="46">
         <f>C28+D28</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
@@ -19081,31 +19081,31 @@
       </c>
       <c r="C29" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B29,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D29" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B29,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="E29" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B29,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F29" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B29,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G29" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B29,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H29" s="17">
         <f>SUM(C29:G29)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="I29" s="46">
         <f>C29+D29</f>
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -19116,31 +19116,31 @@
       </c>
       <c r="C30" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B30,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D30" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B30,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="E30" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B30,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F30" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B30,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G30" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B30,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H30" s="17">
         <f>SUM(C30:G30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="I30" s="46">
         <f>C30+D30</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -19151,31 +19151,31 @@
       </c>
       <c r="C31" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B31,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D31" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B31,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E31" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B31,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F31" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B31,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G31" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B31,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H31" s="17">
         <f>SUM(C31:G31)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I31" s="46">
         <f>C31+D31</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
@@ -19186,31 +19186,31 @@
       </c>
       <c r="C32" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B32,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D32" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B32,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="E32" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B32,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F32" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B32,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G32" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B32,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H32" s="17">
         <f>SUM(C32:G32)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="I32" s="46">
         <f>C32+D32</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -19221,31 +19221,31 @@
       </c>
       <c r="C33" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B33,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D33" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B33,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E33" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B33,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F33" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B33,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G33" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B33,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H33" s="17">
         <f>SUM(C33:G33)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I33" s="46">
         <f>C33+D33</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
@@ -19256,31 +19256,31 @@
       </c>
       <c r="C34" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B34,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D34" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B34,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="E34" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B34,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F34" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B34,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G34" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B34,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H34" s="17">
         <f>SUM(C34:G34)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="I34" s="46">
         <f>C34+D34</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -19291,31 +19291,31 @@
       </c>
       <c r="C35" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B35,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D35" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B35,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="E35" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B35,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F35" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B35,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G35" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B35,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H35" s="17">
         <f>SUM(C35:G35)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I35" s="46">
         <f>C35+D35</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -19326,31 +19326,31 @@
       </c>
       <c r="C36" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B36,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D36" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B36,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E36" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B36,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F36" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B36,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G36" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B36,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H36" s="17">
         <f>SUM(C36:G36)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I36" s="46">
         <f>C36+D36</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
@@ -19361,31 +19361,31 @@
       </c>
       <c r="C37" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B37,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D37" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B37,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E37" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B37,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F37" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B37,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G37" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B37,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H37" s="17">
         <f>SUM(C37:G37)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I37" s="46">
         <f>C37+D37</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -19396,31 +19396,31 @@
       </c>
       <c r="C38" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B38,'2. Matriz de Riesgos'!$L$5:$L$122,"Extremo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D38" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B38,'2. Matriz de Riesgos'!$L$5:$L$122,"Alto")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="E38" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B38,'2. Matriz de Riesgos'!$L$5:$L$122,"Medio")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F38" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B38,'2. Matriz de Riesgos'!$L$5:$L$122,"Bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="46">
         <f>COUNTIFS('2. Matriz de Riesgos'!$B$5:$B$122,$B38,'2. Matriz de Riesgos'!$L$5:$L$122,"Muy bajo")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="17">
         <f>SUM(C38:G38)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I38" s="46">
         <f>C38+D38</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">

--- a/Checklist_Riesgos_Centro_Distribucion.xlsx
+++ b/Checklist_Riesgos_Centro_Distribucion.xlsx
@@ -450,104 +450,98 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="10">
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C00000"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FF974706"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00ED7D31"/>
+        <patternFill>
+          <bgColor rgb="FFFCD5B4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00000000"/>
+        <color rgb="FF9C6500"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFC000"/>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="0070AD47"/>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00000000"/>
+        <color rgb="FF3F3F3F"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00BFBFBF"/>
+        <patternFill>
+          <bgColor rgb="FFE7E6E6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F4B7B7"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
+        <patternFill>
+          <bgColor rgb="FFFCD5B4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFE699"/>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFC000"/>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="FF1F3864"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F4B7B7"/>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -18506,12 +18500,15 @@
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
       <formula>"Cerrada"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="9">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Abierta"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="9">
+      <formula>"En ejecución"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H44">
-    <cfRule type="expression" priority="4" dxfId="5">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND($H5&lt;&gt;"",$I5="",$H5&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19824,12 +19821,12 @@
     <mergeCell ref="C49:D49"/>
   </mergeCells>
   <conditionalFormatting sqref="C24:C38">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="10">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D38">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="6">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Checklist_Riesgos_Centro_Distribucion.xlsx
+++ b/Checklist_Riesgos_Centro_Distribucion.xlsx
@@ -1280,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E105"/>
+  <dimension ref="A2:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1307,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. IDENTIFICACIÓN Y GENERALIDADES</t>
+          <t xml:space="preserve">  1. IDENTIFICACIÓN Y OPERACIÓN</t>
         </is>
       </c>
     </row>
@@ -1338,13 +1338,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="15" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Nombre / código del centro de distribución</t>
+          <t>Nombre / código del CEDI, ciudad y país</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Identifica el activo dentro de la red logística.</t>
+          <t>Define el marco legal aplicable y la amenaza natural y social del sitio.</t>
         </is>
       </c>
     </row>
@@ -1365,18 +1365,18 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Dirección, ciudad y país</t>
+          <t>Año de construcción y de la última ampliación</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr"/>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Define el marco legal aplicable y la amenaza natural y social del sitio.</t>
+          <t>Indica bajo qué código de construcción fue diseñado (norma sísmica vigente en su momento).</t>
         </is>
       </c>
     </row>
@@ -1386,18 +1386,18 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Coordenadas geográficas</t>
+          <t>Tenencia: propio / arrendado / operado por un 3PL</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr"/>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Lat / Long</t>
+          <t>Selección</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Permite cruzar con mapas de amenaza sísmica, inundación y criminalidad.</t>
+          <t>Determina quién responde por la infraestructura y qué se puede modificar.</t>
         </is>
       </c>
     </row>
@@ -1407,18 +1407,18 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Año de construcción y de la última ampliación</t>
+          <t>Turnos y días de operación (24/7, 2 turnos, etc.)</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Año</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Indica bajo qué código de construcción fue diseñado (norma sísmica vigente en su momento).</t>
+          <t>Mayor exposición horaria = mayor probabilidad; obliga a cobertura de brigada por turno.</t>
         </is>
       </c>
     </row>
@@ -1428,356 +1428,327 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Tenencia: propio / arrendado / operado por 3PL</t>
+          <t>Personas: directas / temporales / contratistas</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr"/>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Selección</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Determina quién responde por la infraestructura y qué se puede modificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Certificaciones vigentes (ISO 9001/14001/45001, BASC, OEA, BPM, HACCP)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Evidencia madurez del sistema de gestión y reduce la probabilidad de fallas sistémicas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Turnos y días de operación (24/7, 2 turnos, etc.)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Mayor exposición horaria = mayor probabilidad de eventos; obliga a cobertura de brigada por turno.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Número de personas: directas / temporales / contratistas</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Personas</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Define la magnitud de la consecuencia humana y la carga de inducción y entrenamiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. INFRAESTRUCTURA Y DIMENSIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+          <t>Magnitud de la consecuencia humana y carga de inducción y entrenamiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. EDIFICIO Y PISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Variable a caracterizar</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Valor / respuesta</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Unidad o formato</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Por qué importa para la calificación del riesgo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Área cubierta y número de bodegas o sectores independientes</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>m² / número</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Escala de la pérdida máxima probable; la compartimentación la limita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Altura libre a la viga inferior y altura máxima de almacenamiento</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Por encima de 7,6 m cambian los criterios de protección contra incendio y de estabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Capacidad portante de la losa y clasificación de planitud, con fecha de medición</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>t/m² · TR34 / DIN 15185 / FF-FL</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Restringe la carga puntual de montantes y define si el piso admite la altura de elevación actual.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Área total del lote y área construida cubierta</t>
+          <t>Estado del piso: acabado, juntas, zonas con recubrimiento y programa de resellado</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr"/>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>Texto / fecha</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Escala del impacto potencial y requisitos de sectorización y de protección contra incendio.</t>
+          <t>Las juntas y el acabado deteriorados dañan equipos, generan vibración y contaminan producto.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Número de bodegas o sectores independientes</t>
+          <t>Cubierta: tipo, estado y capacidad del sistema de drenaje</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr"/>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Número</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>La compartimentación limita la propagación y la pérdida máxima probable.</t>
+          <t>Riesgo de colapso por granizo o agua empozada y de daño masivo por filtración.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Altura libre a la viga inferior / a la cubierta</t>
+          <t>Sectorización: muros y puertas cortafuego</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr"/>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Sí / No + descripción</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Determina el tipo de rociador requerido y la severidad de un incendio en altura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
+          <t>Es el control que evita que un incendio se convierta en pérdida total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="39" customHeight="1">
       <c r="A21" s="15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Altura máxima de almacenamiento</t>
+          <t>Zonas especiales: cuarto frío, jaula de valor, MERPEL, inflamables, mezanine, sala de baterías</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr"/>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Por encima de 7,6 m cambian los criterios de protección contra incendio y de estabilidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Capacidad portante de la losa</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr"/>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>t/m² o kN/m²</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Restringe carga puntual de montantes, tránsito de equipos y peso por posición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Clasificación de planitud del piso y fecha de la última medición</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr"/>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>TR34 / DIN 15185 / FF-FL</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Define si el piso admite la altura de elevación y el tipo de pasillo; en pasillo muy estrecho la desviación se amplifica con la altura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Tipo de acabado del piso y recubrimientos por zona</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr"/>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>Determina la resistencia a la abrasión, al ataque químico y al deslizamiento.</t>
+          <t>Cada zona añade riesgos específicos y requisitos legales propios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. VOLUMEN, INVENTARIO Y PRODUCTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Variable a caracterizar</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Valor / respuesta</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Unidad o formato</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Por qué importa para la calificación del riesgo</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Estado de las juntas y programa de resellado</t>
+          <t>Posiciones de estiba instaladas y % de ocupación promedio y pico</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr"/>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Texto / fecha</t>
+          <t>Posiciones / %</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Las juntas deterioradas son la causa más común de daño de equipos y de vibración de la carga en altura.</t>
+          <t>Por encima del 85-90% aparecen bloqueos de pasillos, almacenamiento improvisado y accidentes.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>¿Cámara de congelación con sistema anti-congelamiento del subsuelo?</t>
+          <t>SKU activos y unidades, cajas o pallets movidos por día</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr"/>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Sí / No</t>
+          <t>Número</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Su falla levanta y fisura el piso de la cámara; repararlo exige sacarla de servicio.</t>
+          <t>Complejidad operativa y exposición: a más movimientos, más colisiones, averías y errores.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Tipo de cubierta y sistema de drenaje</t>
+          <t>Rotación del inventario y valor promedio y pico del inventario</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr"/>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Turns/año · moneda</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Riesgo de colapso por granizo o agua empozada y de daño masivo por filtración.</t>
+          <t>Baja rotación concentra valor y carga de fuego; el valor pico se compara contra la póliza.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="15" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Sectorización: muros y puertas cortafuego</t>
+          <t>Estacionalidad: meses pico y % de incremento</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr"/>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Sí / No + descripción</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Es el control que evita que un incendio se convierta en pérdida total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
+          <t>Los picos concentran la accidentalidad, el desorden y el personal sin experiencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="39" customHeight="1">
       <c r="A29" s="15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Zonas especiales: cuarto frío, jaula de valor, MERPEL, inflamables, mezanine</t>
+          <t>Familias de producto y clasificación de mercancía para incendio (Clase I-IV, plásticos, aerosoles)</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr"/>
@@ -1788,1414 +1759,813 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Cada zona añade riesgos específicos y requisitos legales propios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. VOLUMEN, INVENTARIO Y PRODUCTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+          <t>Determina si el sistema de rociadores instalado sigue siendo válido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="A30" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Condiciones especiales: cadena de frío, mercancías peligrosas (clases ONU), alto valor, producto regulado</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr"/>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Activan riesgo sanitario, de hurto, de segregación y de trazabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. SISTEMA DE ALMACENAMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Variable a caracterizar</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Valor / respuesta</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Unidad o formato</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Por qué importa para la calificación del riesgo</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Número de posiciones de estiba (pallet) instaladas</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr"/>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>Posiciones</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>Base para calcular ocupación; la ocupación alta multiplica casi todos los riesgos operativos.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Ocupación promedio y ocupación pico</t>
+          <t>Tipos de estantería, fabricante y año de instalación</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr"/>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Por encima del 85-90% aparecen bloqueos de pasillos, almacenamiento improvisado y accidentes.</t>
+          <t>Cada sistema tiene modos de falla y frecuencias de inspección distintas.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>SKU activos y clasificación ABC</t>
+          <t>¿Existe memoria de cálculo y placas de carga visibles?</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr"/>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Número / %</t>
+          <t>Sí / No / Parcial</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Complejidad operativa, errores de picking y necesidad de conteos cíclicos.</t>
+          <t>Sin memoria no se puede verificar la capacidad; la placa es el control contra la sobrecarga.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Unidades, cajas o pallets movidos por día (entradas y salidas)</t>
+          <t>PRRS designado, fecha de la última inspección experta y daños rojo / ámbar pendientes</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr"/>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>Unid/día</t>
+          <t>Texto / fecha / número</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Throughput = exposición: a más movimientos, más probabilidad de colisión, avería y error.</t>
+          <t>Requisito de EN 15635. Si supera 12 meses o hay daños rojos abiertos, el riesgo sube.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Rotación del inventario (turns/año) y días de inventario</t>
+          <t>Ancho y tipo de pasillo (convencional, estrecho, muy estrecho)</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr"/>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Número</t>
+          <t>m / tipo</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Baja rotación concentra valor y aumenta obsolescencia y carga de fuego permanente.</t>
+          <t>Pasillos estrechos aumentan la probabilidad de impacto contra montantes.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Valor promedio del inventario y valor pico</t>
+          <t>Estibas: tipo, medida y estado; ¿almacenamiento en bloque y a qué altura?</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr"/>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Moneda</t>
+          <t>Texto / m</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Define el impacto económico y debe compararse contra el valor asegurado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Estacionalidad (meses pico y % de incremento)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr"/>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>Los picos son el momento de mayor accidentalidad y desorden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Familias de producto y clasificación de mercancía para incendio (Clase I-IV, plásticos)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr"/>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>Determina si el sistema de rociadores instalado sigue siendo válido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>¿Maneja mercancías peligrosas? Clases ONU presentes</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr"/>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>Sí / No + clases</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Activa requisitos de segregación, rotulado, FDS, kit de derrames y formación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="26" customHeight="1">
+          <t>Causa frecuente de caída de carga desde altura y de volcamiento de rumas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. EQUIPOS DE MANIPULACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Variable a caracterizar</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Valor / respuesta</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Unidad o formato</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Por qué importa para la calificación del riesgo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="39" customHeight="1">
       <c r="A42" s="15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>¿Maneja cadena de frío? Rangos de temperatura</t>
+          <t>Cantidad y tipo de equipos (contrabalanceado, retráctil, apilador, orderpicker, trilateral)</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr"/>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Sí / No + °C</t>
+          <t>Número por tipo</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Añade riesgo de pérdida total del lote por falla de equipo o de energía.</t>
+          <t>Define el perfil de accidentalidad y los programas de mantenimiento y certificación.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="15" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>¿Producto de alto valor o de alto riesgo de hurto?</t>
+          <t>Fuente de energía (eléctrica, GLP, diésel) y edad promedio de la flota</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr"/>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>Sí / No</t>
+          <t>Texto / años</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Define necesidad de jaula, CCTV dedicado y controles de seguridad reforzados.</t>
+          <t>GLP y diésel añaden riesgo de incendio y de CO; las flotas viejas fallan más.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="15" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>¿Alimentos, farmacéuticos o producto regulado?</t>
+          <t>Tecnología de baterías (plomo-ácido / ion-litio) y ubicación de la carga</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr"/>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Sí / No</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Añade riesgo sanitario, trazabilidad, recall y sanción del ente regulador.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. SISTEMA DE ALMACENAMIENTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+          <t>Plomo-ácido: hidrógeno y ácido. Litio: fuga térmica de difícil extinción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Operadores certificados vs. número de equipos y % de cumplimiento del preventivo</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr"/>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Número / %</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>El déficit de operadores obliga a suplencias; el preventivo predice la falla mecánica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. MUELLES Y PATIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Variable a caracterizar</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>Valor / respuesta</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>Unidad o formato</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>Por qué importa para la calificación del riesgo</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="39" customHeight="1">
-      <c r="A48" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Tipos de estantería (selectiva, doble profundidad, drive-in, push back, dinámica, cantilever, automatizada)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr"/>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>Cada sistema tiene modos de falla y frecuencias de inspección distintas.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Fabricante, año de instalación y memoria de cálculo disponible</t>
+          <t>Número de muelles y tipo (a nivel, elevado con nivelador, rampa)</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr"/>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Texto / Sí-No</t>
+          <t>Número / tipo</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Sin memoria de cálculo no hay forma de verificar la capacidad real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
+          <t>Los muelles concentran los accidentes graves con montacargas y camiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
       <c r="A50" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Placas de carga instaladas y visibles</t>
+          <t>¿Dock lock, calzos y semáforos de muelle? Estado del piso frente a los muelles</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr"/>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Sí / No / Parcial</t>
+          <t>Sí / No + texto</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Es el control primario contra la sobrecarga de estantería.</t>
+          <t>Control clave contra el desplazamiento del vehículo y contra el desnivel en la transición.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>¿Existe PRRS designado (responsable de seguridad de estanterías)?</t>
+          <t>Patio: área, capacidad de parqueo, zona de espera de conductores y sistema de citas</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr"/>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>Sí / No + nombre</t>
+          <t>m² / Sí-No</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Requisito de EN 15635 para el ciclo de inspección semanal y el reporte de daños.</t>
+          <t>Patios pequeños y sin citas generan maniobras riesgosas y filas en la vía pública.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Fecha de la última inspección experta de estantería</t>
+          <t>Vehículos atendidos por día y tipo; ¿opera exportación en contenedor?</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr"/>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Número / Sí-No</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Si supera 12 meses, el riesgo de colapso se califica al alza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Nivel de daño acumulado (rojo / ámbar / verde) del último informe</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr"/>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>Número por color</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>Los daños rojos exigen descarga y bloqueo inmediato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Ancho de pasillo de trabajo y tipo de pasillo (convencional, estrecho, muy estrecho)</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr"/>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>Pasillos estrechos aumentan la probabilidad de impacto contra montantes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Tipo, medida y estado de las estibas o pallets</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr"/>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>Estibas deterioradas son causa frecuente de caída de carga desde altura.</t>
+          <t>Define el tránsito interno y activa los requisitos BASC / OEA / C-TPAT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. PROTECCIÓN CONTRA INCENDIO Y SERVICIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Variable a caracterizar</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Valor / respuesta</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Unidad o formato</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Por qué importa para la calificación del riesgo</t>
         </is>
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>¿Almacenamiento en bloque / apilado en piso? Altura máxima</t>
+          <t>Rociadores: tipo (ESFR, techo, in-rack), año y última certificación</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr"/>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>Sí / No + m</t>
+          <t>Texto / fecha</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Riesgo de volcamiento de rumas y de bloqueo de rutas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. EQUIPOS DE MANIPULACIÓN (MHE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>Variable a caracterizar</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Valor / respuesta</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Unidad o formato</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Por qué importa para la calificación del riesgo</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="39" customHeight="1">
+          <t>Es el control decisivo entre un conato y una pérdida total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Reserva de agua y bomba contra incendio: capacidad y última prueba con flujo</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr"/>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>m³ / fecha</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Sin agua suficiente el sistema no cumple su función de diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Detección y alarma, extintores e hidrantes: cobertura y última prueba o recarga</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr"/>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Texto / fecha</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Determina el tiempo de detección y la capacidad de respuesta inicial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="39" customHeight="1">
+      <c r="A59" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Respaldo de energía (planta, UPS): alcance y prueba con carga; última termografía de tableros</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr"/>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>Texto / fecha</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Define qué sobrevive a un corte; la falla eléctrica es causa principal de incendio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
       <c r="A60" s="15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Cantidad y tipo de equipos (contrabalanceado, retráctil, apilador, transpaleta, orderpicker, trilateral)</t>
+          <t>Distancia y tiempo de respuesta de bomberos; hidrantes públicos cercanos</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr"/>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>Número por tipo</t>
+          <t>km / min</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Define el perfil de accidentalidad y los programas de mantenimiento y certificación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Fuente de energía (eléctrica, GLP, diésel) y edad promedio de la flota</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr"/>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t>Texto / años</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>GLP y diésel añaden riesgo de incendio y CO; flotas viejas fallan más.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>¿Sala de carga de baterías? Tecnología (plomo-ácido / ion-litio)</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr"/>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>Sí / No + tipo</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>Plomo-ácido: hidrógeno y ácido. Litio: fuga térmica de difícil extinción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Número de operadores certificados vs. número de equipos</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr"/>
-      <c r="D63" s="15" t="inlineStr">
-        <is>
-          <t>Número</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>Déficit de operadores certificados obliga a suplencias improvisadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="39" customHeight="1">
+          <t>Un tiempo de respuesta alto obliga a mayor autoprotección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. ENTORNO Y AMENAZA NATURAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Variable a caracterizar</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Valor / respuesta</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Unidad o formato</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Por qué importa para la calificación del riesgo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
       <c r="A64" s="15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>¿Sistemas de seguridad instalados (anticolisión, telemetría, limitador de velocidad, luces azules)?</t>
+          <t>Zona de amenaza sísmica y ¿el diseño de la estantería contempló carga sísmica?</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr"/>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Texto / Sí-No-Se desconoce</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Reducen fuertemente la probabilidad de atropellamiento y volcamiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="26" customHeight="1">
+          <t>Sin diseño sísmico, un sismo moderado puede colapsar la estantería llena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="39" customHeight="1">
       <c r="A65" s="15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Cumplimiento del plan de mantenimiento preventivo</t>
+          <t>¿Zona inundable? Nivel del piso respecto a la vía; amenaza por viento, granizo o deslizamiento</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr"/>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Sí / No + texto</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Es el mejor predictor de falla mecánica en operación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. MUELLES, PATIOS Y TRANSPORTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
+          <t>Define si se puede almacenar en piso y los requisitos de cubierta y anclajes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Ocupantes colindantes y actividades peligrosas cercanas</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr"/>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Un siniestro del vecino puede destruir el CEDI o forzar su evacuación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Nivel de criminalidad de la zona, histórico de asalto o hurto y vías de acceso</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr"/>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Modifica el riesgo de seguridad física y los controles exigidos por la aseguradora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9. GESTIÓN, SISTEMAS Y ASEGURAMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Variable a caracterizar</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>Valor / respuesta</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>Unidad o formato</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>Por qué importa para la calificación del riesgo</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Número de muelles de recibo y de despacho</t>
-        </is>
-      </c>
-      <c r="C69" s="16" t="inlineStr"/>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t>Número</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>Define capacidad, congestión y exposición del punto más crítico del CEDI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Tipo de muelle (a nivel, elevado con nivelador, rampa) y capacidad del nivelador</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr"/>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>Texto / kg</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>Los muelles concentran los accidentes graves con montacargas y camiones.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>¿Dock lock, calzos y semáforos de muelle?</t>
+          <t>WMS / ERP y ¿procedimiento manual de contingencia probado?</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr"/>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>Sí / No</t>
+          <t>Texto / fecha</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Control clave contra el desplazamiento del vehículo durante el cargue.</t>
+          <t>Su caída paraliza el 100% de la operación en un CEDI moderno.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Área de patio, capacidad de parqueo y zona de espera de conductores</t>
+          <t>Certificaciones vigentes (ISO 9001/14001/45001, BASC, OEA, BPM, HACCP)</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr"/>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>m² / vehículos</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Patios pequeños generan maniobras riesgosas y filas en la vía pública.</t>
+          <t>Evidencia madurez del sistema de gestión y reduce la probabilidad de fallas sistémicas.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>¿Sistema de citas / agendamiento de vehículos?</t>
+          <t>Póliza: valores asegurados, deducibles y recomendaciones de la aseguradora abiertas</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr"/>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Sí / No</t>
+          <t>Moneda / texto</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Sin citas, el pico de llegadas produce congestión y presión sobre la operación.</t>
+          <t>Define cuánto de la pérdida está realmente transferida; una recomendación abierta puede invalidarla.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Vehículos atendidos por día y tipo (turbo, sencillo, tractomula, contenedor)</t>
+          <t>Eventos de los últimos 5 años (incendio, colapso, accidente, hurto, inundación)</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr"/>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>Número / tipo</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Define el tránsito interno y la exposición peatón-vehículo.</t>
+          <t>La frecuencia histórica es el mejor estimador de la probabilidad futura.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>¿Opera exportación en contenedor?</t>
+          <t>Indicadores actuales (accidentalidad, pérdida desconocida, ERI, averías) y ¿BCP probado?</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr"/>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>Sí / No</t>
+          <t>Números / fecha</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Activa el riesgo de contaminación de la carga y requisitos BASC / OEA / C-TPAT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7. PROTECCIÓN CONTRA INCENDIO Y SERVICIOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>Variable a caracterizar</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Valor / respuesta</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Unidad o formato</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Por qué importa para la calificación del riesgo</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="26" customHeight="1">
-      <c r="A79" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Sistema de rociadores: tipo (ESFR, techo, in-rack), año y última certificación</t>
-        </is>
-      </c>
-      <c r="C79" s="16" t="inlineStr"/>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>Texto / fecha</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>Es el control decisivo entre un conato y una pérdida total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="26" customHeight="1">
-      <c r="A80" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Reserva de agua contra incendio y bomba (tipo y prueba anual)</t>
-        </is>
-      </c>
-      <c r="C80" s="16" t="inlineStr"/>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>m³ / Sí-No</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>Sin agua suficiente el sistema no cumple su función de diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="26" customHeight="1">
-      <c r="A81" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Detección y alarma: cobertura y última prueba funcional</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr"/>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>Texto / fecha</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>Determina el tiempo de detección y de evacuación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="26" customHeight="1">
-      <c r="A82" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Número de extintores, gabinetes e hidrantes; fecha de última recarga</t>
-        </is>
-      </c>
-      <c r="C82" s="16" t="inlineStr"/>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>Número / fecha</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>Primera línea de respuesta ante conato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="26" customHeight="1">
-      <c r="A83" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Distancia y tiempo de respuesta del cuerpo de bomberos; hidrantes públicos cercanos</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="inlineStr"/>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>km / min</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>Un tiempo de respuesta alto obliga a mayor autoprotección.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Subestación (kVA), planta eléctrica y UPS: alcance y prueba con carga</t>
-        </is>
-      </c>
-      <c r="C84" s="16" t="inlineStr"/>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>Define qué sobrevive a un corte de energía: WMS, frío, CCTV, control de acceso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Fecha de la última termografía de tableros eléctricos</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr"/>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>La falla eléctrica es una de las principales causas de incendio en bodegas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8. ENTORNO, AMENAZA NATURAL Y SEGURIDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Variable a caracterizar</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Valor / respuesta</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>Unidad o formato</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>Por qué importa para la calificación del riesgo</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="26" customHeight="1">
-      <c r="A89" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Zona de amenaza sísmica (baja / intermedia / alta) y aceleración de diseño</t>
-        </is>
-      </c>
-      <c r="C89" s="16" t="inlineStr"/>
-      <c r="D89" s="15" t="inlineStr">
-        <is>
-          <t>Texto / Aa</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>Modifica directamente el riesgo de colapso estructural y de estantería.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="26" customHeight="1">
-      <c r="A90" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>¿El diseño de la estantería contempló carga sísmica?</t>
-        </is>
-      </c>
-      <c r="C90" s="16" t="inlineStr"/>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>Sí / No / Se desconoce</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>Sin diseño sísmico, un sismo moderado puede colapsar la estantería llena.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="26" customHeight="1">
-      <c r="A91" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>¿Zona inundable? Nivel del piso respecto a la vía y a cuerpos de agua cercanos</t>
-        </is>
-      </c>
-      <c r="C91" s="16" t="inlineStr"/>
-      <c r="D91" s="15" t="inlineStr">
-        <is>
-          <t>Sí / No + m</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>Define si se puede almacenar producto directamente en piso y el riesgo de pérdida masiva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="26" customHeight="1">
-      <c r="A92" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Amenaza por vientos fuertes, granizo, deslizamiento o incendio forestal</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr"/>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>Determina requisitos de cubierta, anclajes y protocolos de alerta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Ocupantes colindantes y actividades peligrosas cercanas (radio de 500 m)</t>
-        </is>
-      </c>
-      <c r="C93" s="16" t="inlineStr"/>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>Un siniestro del vecino puede destruir el CEDI o forzar su evacuación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="A94" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Nivel de criminalidad de la zona e histórico de asalto o hurto</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="inlineStr"/>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>Modifica el riesgo de seguridad física y los controles exigidos por la aseguradora.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="26" customHeight="1">
-      <c r="A95" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Vías de acceso, restricciones de horario y riesgo de bloqueos</t>
-        </is>
-      </c>
-      <c r="C95" s="16" t="inlineStr"/>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>Afecta continuidad, cumplimiento de entregas y respuesta de emergencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9. GESTIÓN, SISTEMAS Y ASEGURAMIENTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>Variable a caracterizar</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Valor / respuesta</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>Unidad o formato</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>Por qué importa para la calificación del riesgo</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="A99" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>WMS / ERP utilizados y esquema de respaldo y alta disponibilidad</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="inlineStr"/>
-      <c r="D99" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>Su caída paraliza el 100% de la operación en un CEDI moderno.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="26" customHeight="1">
-      <c r="A100" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>¿Procedimiento manual de contingencia probado?</t>
-        </is>
-      </c>
-      <c r="C100" s="16" t="inlineStr"/>
-      <c r="D100" s="15" t="inlineStr">
-        <is>
-          <t>Sí / No + fecha</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>Es la diferencia entre operar degradado y detenerse por completo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="26" customHeight="1">
-      <c r="A101" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>Aseguradora, valores asegurados (edificio, contenido, lucro cesante) y deducibles</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr"/>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>Moneda</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>Define cuánto de la pérdida es realmente transferida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="26" customHeight="1">
-      <c r="A102" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Recomendaciones de la última inspección de la aseguradora y su estado de cierre</t>
-        </is>
-      </c>
-      <c r="C102" s="16" t="inlineStr"/>
-      <c r="D102" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>Recomendaciones abiertas pueden invalidar la indemnización.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="39" customHeight="1">
-      <c r="A103" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Histórico de eventos de los últimos 5 años (incendios, colapsos, accidentes, hurtos, inundaciones)</t>
-        </is>
-      </c>
-      <c r="C103" s="16" t="inlineStr"/>
-      <c r="D103" s="15" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>La frecuencia histórica es el mejor estimador de la probabilidad futura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="26" customHeight="1">
-      <c r="A104" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Indicadores actuales: accidentalidad, pérdida desconocida, ERI, averías, ocupación</t>
-        </is>
-      </c>
-      <c r="C104" s="16" t="inlineStr"/>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>Números</t>
-        </is>
-      </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t>Permiten calificar con datos y no con percepción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="26" customHeight="1">
-      <c r="A105" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>¿Existe plan de continuidad del negocio (BCP) probado?</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr"/>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>Sí / No + fecha</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>Determina el tiempo de recuperación tras un siniestro mayor.</t>
+          <t>Permiten calificar con datos y no con percepción; el BCP define el tiempo de recuperación.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Checklist_Riesgos_Centro_Distribucion.xlsx
+++ b/Checklist_Riesgos_Centro_Distribucion.xlsx
@@ -13120,10 +13120,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="I5:J135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Escala 1 a 5" prompt="Ver la hoja '3. Escalas y Criterios'" type="list">
+    <dataValidation sqref="I5:J135" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no permitido" error="La escala va únicamente de 1 a 5. Consulte los criterios en la hoja '3. Escalas y Criterios'." promptTitle="Escala 1 a 5" prompt="1 Raro · 2 Improbable · 3 Posible · 4 Probable · 5 Casi seguro" type="list" errorStyle="stop">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q5:Q135" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no permitido" error="Seleccione una de las opciones de la lista." type="list" errorStyle="stop">
       <formula1>"Sí,Parcial,No,N.A.,Sin evaluar"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18528,7 +18528,7 @@
     <mergeCell ref="A26:J26"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J6:J131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J6:J131" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no permitido" error="Seleccione una de las opciones de la lista." type="list" errorStyle="stop">
       <formula1>"Al día,Vencida,En ejecución,No aplica"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19298,13 +19298,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no permitido" error="Seleccione una de las opciones de la lista." type="list" errorStyle="stop">
       <formula1>"Correctiva,Preventiva,De mejora,Control de ingeniería,Control administrativo,EPP"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no permitido" error="Seleccione una de las opciones de la lista." type="list" errorStyle="stop">
       <formula1>"Extremo,Alto,Medio,Bajo,Muy bajo"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no permitido" error="Seleccione una de las opciones de la lista." type="list" errorStyle="stop">
       <formula1>"Abierta,En ejecución,Cerrada,Vencida,Cancelada"</formula1>
     </dataValidation>
   </dataValidations>
